--- a/research/traditional_assets/database/data/ivory_coast/ivory_coast_rubber_tires.xlsx
+++ b/research/traditional_assets/database/data/ivory_coast/ivory_coast_rubber_tires.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1171513012449347</v>
+        <v>0.1168921729918223</v>
       </c>
       <c r="C2">
-        <v>269.148410681572</v>
+        <v>267.3730145576664</v>
       </c>
       <c r="D2">
-        <v>250.648410681572</v>
+        <v>251.5620145576664</v>
       </c>
       <c r="E2">
-        <v>-101.9</v>
+        <v>-99.21100000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.689</v>
       </c>
       <c r="G2">
         <v>18.5</v>
@@ -1445,28 +1445,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1352567</v>
       </c>
       <c r="N2">
-        <v>21.97499999999999</v>
+        <v>21.83974329999999</v>
       </c>
       <c r="O2">
-        <v>5.493749999999999</v>
+        <v>5.459935824999999</v>
       </c>
       <c r="P2">
-        <v>16.48125</v>
+        <v>16.379807475</v>
       </c>
       <c r="Q2">
-        <v>34.38124999999999</v>
+        <v>34.279807475</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1171513012449347</v>
+        <v>0.1176918414058812</v>
       </c>
       <c r="T2">
-        <v>0.8547702034345664</v>
+        <v>0.8612457352787677</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>162.4688462752677</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1168921729918223</v>
+        <v>0.11663304473871</v>
       </c>
       <c r="C3">
-        <v>267.3730145576664</v>
+        <v>265.6043029008007</v>
       </c>
       <c r="D3">
-        <v>251.5620145576664</v>
+        <v>252.4823029008007</v>
       </c>
       <c r="E3">
-        <v>-99.21100000000001</v>
+        <v>-96.52200000000001</v>
       </c>
       <c r="F3">
-        <v>2.689</v>
+        <v>5.377999999999999</v>
       </c>
       <c r="G3">
         <v>18.5</v>
@@ -1527,28 +1527,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M3">
-        <v>0.1352567</v>
+        <v>0.2705134</v>
       </c>
       <c r="N3">
-        <v>21.83974329999999</v>
+        <v>21.7044866</v>
       </c>
       <c r="O3">
-        <v>5.459935824999999</v>
+        <v>5.426121649999999</v>
       </c>
       <c r="P3">
-        <v>16.379807475</v>
+        <v>16.27836495</v>
       </c>
       <c r="Q3">
-        <v>34.279807475</v>
+        <v>34.17836495</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1176918414058812</v>
+        <v>0.1182434129986837</v>
       </c>
       <c r="T3">
-        <v>0.8612457352787677</v>
+        <v>0.8678534208340751</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>162.4688462752677</v>
+        <v>81.23442313763384</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.11663304473871</v>
+        <v>0.1163739164855977</v>
       </c>
       <c r="C4">
-        <v>265.6043029008007</v>
+        <v>263.8423493416174</v>
       </c>
       <c r="D4">
-        <v>252.4823029008007</v>
+        <v>253.4093493416174</v>
       </c>
       <c r="E4">
-        <v>-96.52200000000001</v>
+        <v>-93.83300000000001</v>
       </c>
       <c r="F4">
-        <v>5.377999999999999</v>
+        <v>8.066999999999998</v>
       </c>
       <c r="G4">
         <v>18.5</v>
@@ -1609,28 +1609,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M4">
-        <v>0.2705134</v>
+        <v>0.4057700999999999</v>
       </c>
       <c r="N4">
-        <v>21.7044866</v>
+        <v>21.56922989999999</v>
       </c>
       <c r="O4">
-        <v>5.426121649999999</v>
+        <v>5.392307474999998</v>
       </c>
       <c r="P4">
-        <v>16.27836495</v>
+        <v>16.17692242499999</v>
       </c>
       <c r="Q4">
-        <v>34.17836495</v>
+        <v>34.07692242499999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1182434129986837</v>
+        <v>0.1188063572016471</v>
       </c>
       <c r="T4">
-        <v>0.8678534208340751</v>
+        <v>0.8745973473286671</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>81.23442313763384</v>
+        <v>54.15628209175589</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1163739164855977</v>
+        <v>0.1161147882324853</v>
       </c>
       <c r="C5">
-        <v>263.8423493416174</v>
+        <v>262.0872285961507</v>
       </c>
       <c r="D5">
-        <v>253.4093493416174</v>
+        <v>254.3432285961507</v>
       </c>
       <c r="E5">
-        <v>-93.83300000000001</v>
+        <v>-91.14400000000001</v>
       </c>
       <c r="F5">
-        <v>8.066999999999998</v>
+        <v>10.756</v>
       </c>
       <c r="G5">
         <v>18.5</v>
@@ -1691,28 +1691,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M5">
-        <v>0.4057700999999999</v>
+        <v>0.5410267999999999</v>
       </c>
       <c r="N5">
-        <v>21.56922989999999</v>
+        <v>21.43397319999999</v>
       </c>
       <c r="O5">
-        <v>5.392307474999998</v>
+        <v>5.358493299999998</v>
       </c>
       <c r="P5">
-        <v>16.17692242499999</v>
+        <v>16.07547989999999</v>
       </c>
       <c r="Q5">
-        <v>34.07692242499999</v>
+        <v>33.9754799</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1188063572016471</v>
+        <v>0.1193810294088389</v>
       </c>
       <c r="T5">
-        <v>0.8745973473286671</v>
+        <v>0.8814817722918966</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>54.15628209175589</v>
+        <v>40.61721156881692</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1161147882324853</v>
+        <v>0.115855659979373</v>
       </c>
       <c r="C6">
-        <v>262.0872285961507</v>
+        <v>260.3390164859013</v>
       </c>
       <c r="D6">
-        <v>254.3432285961507</v>
+        <v>255.2840164859012</v>
       </c>
       <c r="E6">
-        <v>-91.14400000000001</v>
+        <v>-88.45500000000001</v>
       </c>
       <c r="F6">
-        <v>10.756</v>
+        <v>13.445</v>
       </c>
       <c r="G6">
         <v>18.5</v>
@@ -1773,28 +1773,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M6">
-        <v>0.5410267999999999</v>
+        <v>0.6762834999999999</v>
       </c>
       <c r="N6">
-        <v>21.43397319999999</v>
+        <v>21.29871649999999</v>
       </c>
       <c r="O6">
-        <v>5.358493299999998</v>
+        <v>5.324679124999999</v>
       </c>
       <c r="P6">
-        <v>16.07547989999999</v>
+        <v>15.97403737499999</v>
       </c>
       <c r="Q6">
-        <v>33.9754799</v>
+        <v>33.87403737499999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1193810294088389</v>
+        <v>0.1199677999782874</v>
       </c>
       <c r="T6">
-        <v>0.8814817722918966</v>
+        <v>0.8885111325175099</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.61721156881692</v>
+        <v>32.49376925505354</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.115855659979373</v>
+        <v>0.1155965317262607</v>
       </c>
       <c r="C7">
-        <v>260.3390164859013</v>
+        <v>258.597789958356</v>
       </c>
       <c r="D7">
-        <v>255.2840164859012</v>
+        <v>256.231789958356</v>
       </c>
       <c r="E7">
-        <v>-88.45500000000001</v>
+        <v>-85.76600000000001</v>
       </c>
       <c r="F7">
-        <v>13.445</v>
+        <v>16.134</v>
       </c>
       <c r="G7">
         <v>18.5</v>
@@ -1855,28 +1855,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M7">
-        <v>0.6762834999999999</v>
+        <v>0.8115401999999999</v>
       </c>
       <c r="N7">
-        <v>21.29871649999999</v>
+        <v>21.16345979999999</v>
       </c>
       <c r="O7">
-        <v>5.324679124999999</v>
+        <v>5.290864949999999</v>
       </c>
       <c r="P7">
-        <v>15.97403737499999</v>
+        <v>15.87259485</v>
       </c>
       <c r="Q7">
-        <v>33.87403737499999</v>
+        <v>33.77259484999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1199677999782874</v>
+        <v>0.1205670550279369</v>
       </c>
       <c r="T7">
-        <v>0.8885111325175099</v>
+        <v>0.8956900535989871</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.49376925505354</v>
+        <v>27.07814104587795</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1155965317262607</v>
+        <v>0.1153374034731483</v>
       </c>
       <c r="C8">
-        <v>258.597789958356</v>
+        <v>256.8636271079684</v>
       </c>
       <c r="D8">
-        <v>256.231789958356</v>
+        <v>257.1866271079684</v>
       </c>
       <c r="E8">
-        <v>-85.76600000000001</v>
+        <v>-83.07700000000001</v>
       </c>
       <c r="F8">
-        <v>16.134</v>
+        <v>18.823</v>
       </c>
       <c r="G8">
         <v>18.5</v>
@@ -1937,28 +1937,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M8">
-        <v>0.8115401999999998</v>
+        <v>0.9467968999999998</v>
       </c>
       <c r="N8">
-        <v>21.16345979999999</v>
+        <v>21.0282031</v>
       </c>
       <c r="O8">
-        <v>5.290864949999999</v>
+        <v>5.257050774999999</v>
       </c>
       <c r="P8">
-        <v>15.87259485</v>
+        <v>15.771152325</v>
       </c>
       <c r="Q8">
-        <v>33.77259484999999</v>
+        <v>33.67115232499999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1205670550279369</v>
+        <v>0.1211791972829552</v>
       </c>
       <c r="T8">
-        <v>0.8956900535989871</v>
+        <v>0.9030233600800661</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.07814104587795</v>
+        <v>23.2098351821811</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1153374034731483</v>
+        <v>0.115078275220036</v>
       </c>
       <c r="C9">
-        <v>256.8636271079685</v>
+        <v>255.1366071976093</v>
       </c>
       <c r="D9">
-        <v>257.1866271079684</v>
+        <v>258.1486071976093</v>
       </c>
       <c r="E9">
-        <v>-83.077</v>
+        <v>-80.38800000000001</v>
       </c>
       <c r="F9">
-        <v>18.823</v>
+        <v>21.512</v>
       </c>
       <c r="G9">
         <v>18.5</v>
@@ -2019,28 +2019,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M9">
-        <v>0.9467968999999999</v>
+        <v>1.0820536</v>
       </c>
       <c r="N9">
-        <v>21.0282031</v>
+        <v>20.8929464</v>
       </c>
       <c r="O9">
-        <v>5.257050774999999</v>
+        <v>5.223236599999999</v>
       </c>
       <c r="P9">
-        <v>15.771152325</v>
+        <v>15.6697098</v>
       </c>
       <c r="Q9">
-        <v>33.67115232499999</v>
+        <v>33.5697098</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1211791972829552</v>
+        <v>0.1218046469783</v>
       </c>
       <c r="T9">
-        <v>0.9030233600800661</v>
+        <v>0.9105160862672557</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.2098351821811</v>
+        <v>20.30860578440846</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.115078275220036</v>
+        <v>0.1148191469669237</v>
       </c>
       <c r="C10">
-        <v>255.1366071976093</v>
+        <v>253.4168106805003</v>
       </c>
       <c r="D10">
-        <v>258.1486071976093</v>
+        <v>259.1178106805003</v>
       </c>
       <c r="E10">
-        <v>-80.38800000000001</v>
+        <v>-77.69900000000001</v>
       </c>
       <c r="F10">
-        <v>21.512</v>
+        <v>24.201</v>
       </c>
       <c r="G10">
         <v>18.5</v>
@@ -2101,28 +2101,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M10">
-        <v>1.0820536</v>
+        <v>1.2173103</v>
       </c>
       <c r="N10">
-        <v>20.8929464</v>
+        <v>20.75768969999999</v>
       </c>
       <c r="O10">
-        <v>5.223236599999999</v>
+        <v>5.189422424999998</v>
       </c>
       <c r="P10">
-        <v>15.6697098</v>
+        <v>15.56826727499999</v>
       </c>
       <c r="Q10">
-        <v>33.5697098</v>
+        <v>33.468267275</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1218046469783</v>
+        <v>0.1224438428207952</v>
       </c>
       <c r="T10">
-        <v>0.9105160862672557</v>
+        <v>0.9181734877552623</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.30860578440846</v>
+        <v>18.05209403058529</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1148191469669237</v>
+        <v>0.1145600187138113</v>
       </c>
       <c r="C11">
-        <v>253.4168106805003</v>
+        <v>251.7043192226431</v>
       </c>
       <c r="D11">
-        <v>259.1178106805003</v>
+        <v>260.094319222643</v>
       </c>
       <c r="E11">
-        <v>-77.69900000000001</v>
+        <v>-75.01000000000001</v>
       </c>
       <c r="F11">
-        <v>24.201</v>
+        <v>26.89</v>
       </c>
       <c r="G11">
         <v>18.5</v>
@@ -2183,28 +2183,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M11">
-        <v>1.2173103</v>
+        <v>1.352567</v>
       </c>
       <c r="N11">
-        <v>20.75768969999999</v>
+        <v>20.62243299999999</v>
       </c>
       <c r="O11">
-        <v>5.189422424999998</v>
+        <v>5.155608249999998</v>
       </c>
       <c r="P11">
-        <v>15.56826727499999</v>
+        <v>15.46682475</v>
       </c>
       <c r="Q11">
-        <v>33.468267275</v>
+        <v>33.36682474999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1224438428207952</v>
+        <v>0.1230972430153459</v>
       </c>
       <c r="T11">
-        <v>0.9181734877552623</v>
+        <v>0.9260010537207802</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.05209403058529</v>
+        <v>16.24688462752677</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1145600187138113</v>
+        <v>0.114300890460699</v>
       </c>
       <c r="C12">
-        <v>251.7043192226431</v>
+        <v>249.9992157257589</v>
       </c>
       <c r="D12">
-        <v>260.094319222643</v>
+        <v>261.0782157257589</v>
       </c>
       <c r="E12">
-        <v>-75.01000000000001</v>
+        <v>-72.32100000000001</v>
       </c>
       <c r="F12">
-        <v>26.89</v>
+        <v>29.579</v>
       </c>
       <c r="G12">
         <v>18.5</v>
@@ -2265,28 +2265,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M12">
-        <v>1.352567</v>
+        <v>1.4878237</v>
       </c>
       <c r="N12">
-        <v>20.62243299999999</v>
+        <v>20.48717629999999</v>
       </c>
       <c r="O12">
-        <v>5.155608249999998</v>
+        <v>5.121794074999999</v>
       </c>
       <c r="P12">
-        <v>15.46682475</v>
+        <v>15.365382225</v>
       </c>
       <c r="Q12">
-        <v>33.36682474999999</v>
+        <v>33.265382225</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1230972430153459</v>
+        <v>0.1237653263603359</v>
       </c>
       <c r="T12">
-        <v>0.9260010537207802</v>
+        <v>0.9340045200450741</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.24688462752677</v>
+        <v>14.76989511593342</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.114300890460699</v>
+        <v>0.1140417622075867</v>
       </c>
       <c r="C13">
-        <v>249.9992157257589</v>
+        <v>248.3015843507499</v>
       </c>
       <c r="D13">
-        <v>261.0782157257589</v>
+        <v>262.0695843507499</v>
       </c>
       <c r="E13">
-        <v>-72.32100000000001</v>
+        <v>-69.63200000000001</v>
       </c>
       <c r="F13">
-        <v>29.579</v>
+        <v>32.26799999999999</v>
       </c>
       <c r="G13">
         <v>18.5</v>
@@ -2347,28 +2347,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M13">
-        <v>1.4878237</v>
+        <v>1.6230804</v>
       </c>
       <c r="N13">
-        <v>20.48717629999999</v>
+        <v>20.3519196</v>
       </c>
       <c r="O13">
-        <v>5.121794074999999</v>
+        <v>5.087979899999999</v>
       </c>
       <c r="P13">
-        <v>15.365382225</v>
+        <v>15.2639397</v>
       </c>
       <c r="Q13">
-        <v>33.265382225</v>
+        <v>33.16393969999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1237653263603359</v>
+        <v>0.1244485934177121</v>
       </c>
       <c r="T13">
-        <v>0.9340045200450741</v>
+        <v>0.9421898833312835</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.76989511593342</v>
+        <v>13.53907052293897</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1140417622075867</v>
+        <v>0.1139288839544743</v>
       </c>
       <c r="C14">
-        <v>248.3015843507499</v>
+        <v>246.0467901553711</v>
       </c>
       <c r="D14">
-        <v>262.0695843507499</v>
+        <v>262.5037901553711</v>
       </c>
       <c r="E14">
-        <v>-69.63200000000001</v>
+        <v>-66.94300000000001</v>
       </c>
       <c r="F14">
-        <v>32.26799999999999</v>
+        <v>34.957</v>
       </c>
       <c r="G14">
         <v>18.5</v>
@@ -2429,45 +2429,45 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M14">
-        <v>1.6230804</v>
+        <v>1.8107726</v>
       </c>
       <c r="N14">
-        <v>20.3519196</v>
+        <v>20.16422739999999</v>
       </c>
       <c r="O14">
-        <v>5.087979899999999</v>
+        <v>5.041056849999999</v>
       </c>
       <c r="P14">
-        <v>15.2639397</v>
+        <v>15.12317055</v>
       </c>
       <c r="Q14">
-        <v>33.16393969999999</v>
+        <v>33.02317055</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1244485934177121</v>
+        <v>0.1251475677637636</v>
       </c>
       <c r="T14">
-        <v>0.9421898833312835</v>
+        <v>0.9505634158884402</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.53907052293897</v>
+        <v>12.1357038426581</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1139288839544743</v>
+        <v>0.113681005701362</v>
       </c>
       <c r="C15">
-        <v>246.0467901553711</v>
+        <v>244.3163643583719</v>
       </c>
       <c r="D15">
-        <v>262.5037901553711</v>
+        <v>263.4623643583719</v>
       </c>
       <c r="E15">
-        <v>-66.94300000000001</v>
+        <v>-64.254</v>
       </c>
       <c r="F15">
-        <v>34.957</v>
+        <v>37.646</v>
       </c>
       <c r="G15">
         <v>18.5</v>
@@ -2511,28 +2511,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M15">
-        <v>1.8107726</v>
+        <v>1.9500628</v>
       </c>
       <c r="N15">
-        <v>20.16422739999999</v>
+        <v>20.02493719999999</v>
       </c>
       <c r="O15">
-        <v>5.041056849999999</v>
+        <v>5.006234299999998</v>
       </c>
       <c r="P15">
-        <v>15.12317055</v>
+        <v>15.01870289999999</v>
       </c>
       <c r="Q15">
-        <v>33.02317055</v>
+        <v>32.91870289999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1251475677637636</v>
+        <v>0.1258627973271651</v>
       </c>
       <c r="T15">
-        <v>0.9505634158884402</v>
+        <v>0.9591316817608798</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.1357038426581</v>
+        <v>11.2688678538968</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.113681005701362</v>
+        <v>0.1134331274482496</v>
       </c>
       <c r="C16">
-        <v>244.3163643583719</v>
+        <v>242.592964990813</v>
       </c>
       <c r="D16">
-        <v>263.4623643583719</v>
+        <v>264.4279649908131</v>
       </c>
       <c r="E16">
-        <v>-64.254</v>
+        <v>-61.565</v>
       </c>
       <c r="F16">
-        <v>37.646</v>
+        <v>40.335</v>
       </c>
       <c r="G16">
         <v>18.5</v>
@@ -2593,28 +2593,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M16">
-        <v>1.9500628</v>
+        <v>2.089353</v>
       </c>
       <c r="N16">
-        <v>20.02493719999999</v>
+        <v>19.885647</v>
       </c>
       <c r="O16">
-        <v>5.006234299999998</v>
+        <v>4.971411749999999</v>
       </c>
       <c r="P16">
-        <v>15.01870289999999</v>
+        <v>14.91423525</v>
       </c>
       <c r="Q16">
-        <v>32.91870289999999</v>
+        <v>32.81423525</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1258627973271651</v>
+        <v>0.1265948558214701</v>
       </c>
       <c r="T16">
-        <v>0.9591316817608798</v>
+        <v>0.9679015538891413</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.2688678538968</v>
+        <v>10.51760999697035</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1134331274482496</v>
+        <v>0.1131852491951373</v>
       </c>
       <c r="C17">
-        <v>242.5929649908131</v>
+        <v>240.8766695933613</v>
       </c>
       <c r="D17">
-        <v>264.4279649908131</v>
+        <v>265.4006695933613</v>
       </c>
       <c r="E17">
-        <v>-61.56500000000001</v>
+        <v>-58.87600000000001</v>
       </c>
       <c r="F17">
-        <v>40.33499999999999</v>
+        <v>43.02399999999999</v>
       </c>
       <c r="G17">
         <v>18.5</v>
@@ -2675,28 +2675,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M17">
-        <v>2.089353</v>
+        <v>2.2286432</v>
       </c>
       <c r="N17">
-        <v>19.885647</v>
+        <v>19.74635679999999</v>
       </c>
       <c r="O17">
-        <v>4.971411749999999</v>
+        <v>4.936589199999998</v>
       </c>
       <c r="P17">
-        <v>14.91423525</v>
+        <v>14.8097676</v>
       </c>
       <c r="Q17">
-        <v>32.81423525</v>
+        <v>32.70976759999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1265948558214701</v>
+        <v>0.1273443442799254</v>
       </c>
       <c r="T17">
-        <v>0.9679015538891413</v>
+        <v>0.9768802324966473</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.51760999697035</v>
+        <v>9.860259372159705</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1131852491951373</v>
+        <v>0.113154120942025</v>
       </c>
       <c r="C18">
-        <v>240.8766695933613</v>
+        <v>238.3103266647288</v>
       </c>
       <c r="D18">
-        <v>265.4006695933613</v>
+        <v>265.5233266647288</v>
       </c>
       <c r="E18">
-        <v>-58.87600000000001</v>
+        <v>-56.187</v>
       </c>
       <c r="F18">
-        <v>43.02399999999999</v>
+        <v>45.713</v>
       </c>
       <c r="G18">
         <v>18.5</v>
@@ -2757,45 +2757,45 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M18">
-        <v>2.2286432</v>
+        <v>2.4456455</v>
       </c>
       <c r="N18">
-        <v>19.74635679999999</v>
+        <v>19.52935449999999</v>
       </c>
       <c r="O18">
-        <v>4.936589199999998</v>
+        <v>4.882338624999998</v>
       </c>
       <c r="P18">
-        <v>14.8097676</v>
+        <v>14.64701587499999</v>
       </c>
       <c r="Q18">
-        <v>32.70976759999999</v>
+        <v>32.54701587499999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1273443442799254</v>
+        <v>0.1281118927012349</v>
       </c>
       <c r="T18">
-        <v>0.9768802324966473</v>
+        <v>0.9860752648055391</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.860259372159705</v>
+        <v>8.98535785337654</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.113154120942025</v>
+        <v>0.1129189926889126</v>
       </c>
       <c r="C19">
-        <v>238.3103266647288</v>
+        <v>236.5514961064638</v>
       </c>
       <c r="D19">
-        <v>265.5233266647288</v>
+        <v>266.4534961064638</v>
       </c>
       <c r="E19">
-        <v>-56.187</v>
+        <v>-53.498</v>
       </c>
       <c r="F19">
-        <v>45.713</v>
+        <v>48.402</v>
       </c>
       <c r="G19">
         <v>18.5</v>
@@ -2839,28 +2839,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M19">
-        <v>2.4456455</v>
+        <v>2.589507</v>
       </c>
       <c r="N19">
-        <v>19.52935449999999</v>
+        <v>19.38549299999999</v>
       </c>
       <c r="O19">
-        <v>4.882338624999998</v>
+        <v>4.846373249999998</v>
       </c>
       <c r="P19">
-        <v>14.64701587499999</v>
+        <v>14.53911974999999</v>
       </c>
       <c r="Q19">
-        <v>32.54701587499999</v>
+        <v>32.43911974999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1281118927012349</v>
+        <v>0.1288981618157471</v>
       </c>
       <c r="T19">
-        <v>0.9860752648055391</v>
+        <v>0.9954945661951352</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.98535785337654</v>
+        <v>8.486171305966732</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1129189926889126</v>
+        <v>0.1126838644358003</v>
       </c>
       <c r="C20">
-        <v>236.5514961064638</v>
+        <v>234.7992055146846</v>
       </c>
       <c r="D20">
-        <v>266.4534961064638</v>
+        <v>267.3902055146846</v>
       </c>
       <c r="E20">
-        <v>-53.49800000000001</v>
+        <v>-50.80900000000001</v>
       </c>
       <c r="F20">
-        <v>48.40199999999999</v>
+        <v>51.09099999999999</v>
       </c>
       <c r="G20">
         <v>18.5</v>
@@ -2921,28 +2921,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M20">
-        <v>2.589507</v>
+        <v>2.7333685</v>
       </c>
       <c r="N20">
-        <v>19.38549299999999</v>
+        <v>19.24163149999999</v>
       </c>
       <c r="O20">
-        <v>4.846373249999998</v>
+        <v>4.810407874999998</v>
       </c>
       <c r="P20">
-        <v>14.53911974999999</v>
+        <v>14.43122362499999</v>
       </c>
       <c r="Q20">
-        <v>32.43911974999999</v>
+        <v>32.33122362499999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1288981618157471</v>
+        <v>0.1297038449824695</v>
       </c>
       <c r="T20">
-        <v>0.9954945661951352</v>
+        <v>1.005146442927685</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.486171305966732</v>
+        <v>8.039530710915852</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1126838644358003</v>
+        <v>0.112448736182688</v>
       </c>
       <c r="C21">
-        <v>234.7992055146846</v>
+        <v>233.0535241058982</v>
       </c>
       <c r="D21">
-        <v>267.3902055146846</v>
+        <v>268.3335241058982</v>
       </c>
       <c r="E21">
-        <v>-50.80900000000001</v>
+        <v>-48.12</v>
       </c>
       <c r="F21">
-        <v>51.09099999999999</v>
+        <v>53.78</v>
       </c>
       <c r="G21">
         <v>18.5</v>
@@ -3003,28 +3003,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M21">
-        <v>2.7333685</v>
+        <v>2.87723</v>
       </c>
       <c r="N21">
-        <v>19.24163149999999</v>
+        <v>19.09776999999999</v>
       </c>
       <c r="O21">
-        <v>4.810407874999998</v>
+        <v>4.774442499999998</v>
       </c>
       <c r="P21">
-        <v>14.43122362499999</v>
+        <v>14.32332749999999</v>
       </c>
       <c r="Q21">
-        <v>32.33122362499999</v>
+        <v>32.2233275</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1297038449824695</v>
+        <v>0.1305296702283599</v>
       </c>
       <c r="T21">
-        <v>1.005146442927685</v>
+        <v>1.015039616578548</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.039530710915852</v>
+        <v>7.637554175370059</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.112448736182688</v>
+        <v>0.1123396079295756</v>
       </c>
       <c r="C22">
-        <v>233.0535241058982</v>
+        <v>230.8046043776087</v>
       </c>
       <c r="D22">
-        <v>268.3335241058982</v>
+        <v>268.7736043776087</v>
       </c>
       <c r="E22">
-        <v>-48.12</v>
+        <v>-45.431</v>
       </c>
       <c r="F22">
-        <v>53.78</v>
+        <v>56.469</v>
       </c>
       <c r="G22">
         <v>18.5</v>
@@ -3085,45 +3085,45 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M22">
-        <v>2.87723</v>
+        <v>3.0662667</v>
       </c>
       <c r="N22">
-        <v>19.09776999999999</v>
+        <v>18.90873329999999</v>
       </c>
       <c r="O22">
-        <v>4.774442499999998</v>
+        <v>4.727183324999999</v>
       </c>
       <c r="P22">
-        <v>14.32332749999999</v>
+        <v>14.181549975</v>
       </c>
       <c r="Q22">
-        <v>32.2233275</v>
+        <v>32.08154997499999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1305296702283599</v>
+        <v>0.1313764024425008</v>
       </c>
       <c r="T22">
-        <v>1.015039616578548</v>
+        <v>1.025183250321838</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.637554175370059</v>
+        <v>7.166695578046095</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1123396079295756</v>
+        <v>0.1121104796764633</v>
       </c>
       <c r="C23">
-        <v>230.8046043776087</v>
+        <v>229.0443207246209</v>
       </c>
       <c r="D23">
-        <v>268.7736043776087</v>
+        <v>269.7023207246208</v>
       </c>
       <c r="E23">
-        <v>-45.43100000000001</v>
+        <v>-42.74200000000001</v>
       </c>
       <c r="F23">
-        <v>56.46899999999999</v>
+        <v>59.15799999999999</v>
       </c>
       <c r="G23">
         <v>18.5</v>
@@ -3167,28 +3167,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M23">
-        <v>3.0662667</v>
+        <v>3.2122794</v>
       </c>
       <c r="N23">
-        <v>18.90873329999999</v>
+        <v>18.76272059999999</v>
       </c>
       <c r="O23">
-        <v>4.727183324999999</v>
+        <v>4.690680149999999</v>
       </c>
       <c r="P23">
-        <v>14.181549975</v>
+        <v>14.07204045</v>
       </c>
       <c r="Q23">
-        <v>32.08154997499999</v>
+        <v>31.97204044999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1313764024425008</v>
+        <v>0.1322448457390555</v>
       </c>
       <c r="T23">
-        <v>1.025183250321838</v>
+        <v>1.035586977238032</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.166695578046096</v>
+        <v>6.84093668813491</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1121104796764633</v>
+        <v>0.111881351423351</v>
       </c>
       <c r="C24">
-        <v>229.0443207246209</v>
+        <v>227.2904774712206</v>
       </c>
       <c r="D24">
-        <v>269.7023207246208</v>
+        <v>270.6374774712206</v>
       </c>
       <c r="E24">
-        <v>-42.74200000000001</v>
+        <v>-40.05300000000001</v>
       </c>
       <c r="F24">
-        <v>59.15799999999999</v>
+        <v>61.84699999999999</v>
       </c>
       <c r="G24">
         <v>18.5</v>
@@ -3249,28 +3249,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M24">
-        <v>3.2122794</v>
+        <v>3.3582921</v>
       </c>
       <c r="N24">
-        <v>18.76272059999999</v>
+        <v>18.61670789999999</v>
       </c>
       <c r="O24">
-        <v>4.690680149999999</v>
+        <v>4.654176974999999</v>
       </c>
       <c r="P24">
-        <v>14.07204045</v>
+        <v>13.962530925</v>
       </c>
       <c r="Q24">
-        <v>31.97204044999999</v>
+        <v>31.86253092499999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1322448457390555</v>
+        <v>0.1331358460043519</v>
       </c>
       <c r="T24">
-        <v>1.035586977238032</v>
+        <v>1.046260930827375</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.84093668813491</v>
+        <v>6.543504658216</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.111881351423351</v>
+        <v>0.1116522231702386</v>
       </c>
       <c r="C25">
-        <v>227.2904774712206</v>
+        <v>225.5431418441818</v>
       </c>
       <c r="D25">
-        <v>270.6374774712206</v>
+        <v>271.5791418441818</v>
       </c>
       <c r="E25">
-        <v>-40.05300000000001</v>
+        <v>-37.364</v>
       </c>
       <c r="F25">
-        <v>61.84699999999999</v>
+        <v>64.536</v>
       </c>
       <c r="G25">
         <v>18.5</v>
@@ -3331,28 +3331,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M25">
-        <v>3.3582921</v>
+        <v>3.5043048</v>
       </c>
       <c r="N25">
-        <v>18.61670789999999</v>
+        <v>18.47069519999999</v>
       </c>
       <c r="O25">
-        <v>4.654176974999999</v>
+        <v>4.617673799999999</v>
       </c>
       <c r="P25">
-        <v>13.962530925</v>
+        <v>13.8530214</v>
       </c>
       <c r="Q25">
-        <v>31.86253092499999</v>
+        <v>31.75302139999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1331358460043519</v>
+        <v>0.1340502936450508</v>
       </c>
       <c r="T25">
-        <v>1.046260930827375</v>
+        <v>1.057215777932227</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.543504658216</v>
+        <v>6.270858630790333</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1116522231702386</v>
+        <v>0.1116105949171263</v>
       </c>
       <c r="C26">
-        <v>225.5431418441818</v>
+        <v>223.025928245307</v>
       </c>
       <c r="D26">
-        <v>271.5791418441818</v>
+        <v>271.750928245307</v>
       </c>
       <c r="E26">
-        <v>-37.36400000000002</v>
+        <v>-34.67500000000001</v>
       </c>
       <c r="F26">
-        <v>64.53599999999999</v>
+        <v>67.22499999999999</v>
       </c>
       <c r="G26">
         <v>18.5</v>
@@ -3413,45 +3413,45 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M26">
-        <v>3.504304799999999</v>
+        <v>3.7175425</v>
       </c>
       <c r="N26">
-        <v>18.47069519999999</v>
+        <v>18.25745749999999</v>
       </c>
       <c r="O26">
-        <v>4.617673799999999</v>
+        <v>4.564364374999998</v>
       </c>
       <c r="P26">
-        <v>13.8530214</v>
+        <v>13.693093125</v>
       </c>
       <c r="Q26">
-        <v>31.75302139999999</v>
+        <v>31.593093125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1340502936450508</v>
+        <v>0.1349891265561684</v>
       </c>
       <c r="T26">
-        <v>1.057215777932227</v>
+        <v>1.068462754293208</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.270858630790334</v>
+        <v>5.911163086904856</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1116105949171263</v>
+        <v>0.1113889666640139</v>
       </c>
       <c r="C27">
-        <v>223.025928245307</v>
+        <v>221.2551876198934</v>
       </c>
       <c r="D27">
-        <v>271.750928245307</v>
+        <v>272.6691876198934</v>
       </c>
       <c r="E27">
-        <v>-34.67500000000001</v>
+        <v>-31.986</v>
       </c>
       <c r="F27">
-        <v>67.22499999999999</v>
+        <v>69.914</v>
       </c>
       <c r="G27">
         <v>18.5</v>
@@ -3495,28 +3495,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M27">
-        <v>3.7175425</v>
+        <v>3.8662442</v>
       </c>
       <c r="N27">
-        <v>18.25745749999999</v>
+        <v>18.10875579999999</v>
       </c>
       <c r="O27">
-        <v>4.564364374999998</v>
+        <v>4.527188949999998</v>
       </c>
       <c r="P27">
-        <v>13.693093125</v>
+        <v>13.58156684999999</v>
       </c>
       <c r="Q27">
-        <v>31.593093125</v>
+        <v>31.48156684999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1349891265561684</v>
+        <v>0.1359533333297486</v>
       </c>
       <c r="T27">
-        <v>1.068462754293208</v>
+        <v>1.08001370298827</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.911163086904856</v>
+        <v>5.683810660485438</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1113889666640139</v>
+        <v>0.1111673384109016</v>
       </c>
       <c r="C28">
-        <v>221.2551876198934</v>
+        <v>219.4906737195091</v>
       </c>
       <c r="D28">
-        <v>272.6691876198934</v>
+        <v>273.5936737195091</v>
       </c>
       <c r="E28">
-        <v>-31.986</v>
+        <v>-29.29700000000001</v>
       </c>
       <c r="F28">
-        <v>69.914</v>
+        <v>72.60299999999999</v>
       </c>
       <c r="G28">
         <v>18.5</v>
@@ -3577,28 +3577,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M28">
-        <v>3.8662442</v>
+        <v>4.0149459</v>
       </c>
       <c r="N28">
-        <v>18.10875579999999</v>
+        <v>17.96005409999999</v>
       </c>
       <c r="O28">
-        <v>4.527188949999998</v>
+        <v>4.490013524999998</v>
       </c>
       <c r="P28">
-        <v>13.58156684999999</v>
+        <v>13.470040575</v>
       </c>
       <c r="Q28">
-        <v>31.48156684999999</v>
+        <v>31.37004057499999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1359533333297486</v>
+        <v>0.1369439567272625</v>
       </c>
       <c r="T28">
-        <v>1.08001370298827</v>
+        <v>1.091881116031141</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.683810660485438</v>
+        <v>5.473299154541533</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1111673384109016</v>
+        <v>0.1109457101577893</v>
       </c>
       <c r="C29">
-        <v>219.4906737195091</v>
+        <v>217.7324500948403</v>
       </c>
       <c r="D29">
-        <v>273.5936737195091</v>
+        <v>274.5244500948403</v>
       </c>
       <c r="E29">
-        <v>-29.29700000000001</v>
+        <v>-26.608</v>
       </c>
       <c r="F29">
-        <v>72.60299999999999</v>
+        <v>75.292</v>
       </c>
       <c r="G29">
         <v>18.5</v>
@@ -3659,28 +3659,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M29">
-        <v>4.0149459</v>
+        <v>4.1636476</v>
       </c>
       <c r="N29">
-        <v>17.96005409999999</v>
+        <v>17.81135239999999</v>
       </c>
       <c r="O29">
-        <v>4.490013524999998</v>
+        <v>4.452838099999998</v>
       </c>
       <c r="P29">
-        <v>13.470040575</v>
+        <v>13.3585143</v>
       </c>
       <c r="Q29">
-        <v>31.37004057499999</v>
+        <v>31.25851429999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1369439567272625</v>
+        <v>0.137962097441374</v>
       </c>
       <c r="T29">
-        <v>1.091881116031141</v>
+        <v>1.104078179436315</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.473299154541533</v>
+        <v>5.277824184736478</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1109457101577893</v>
+        <v>0.1107240819046769</v>
       </c>
       <c r="C30">
-        <v>217.7324500948403</v>
+        <v>215.9805811643328</v>
       </c>
       <c r="D30">
-        <v>274.5244500948403</v>
+        <v>275.4615811643328</v>
       </c>
       <c r="E30">
-        <v>-26.608</v>
+        <v>-23.919</v>
       </c>
       <c r="F30">
-        <v>75.292</v>
+        <v>77.98100000000001</v>
       </c>
       <c r="G30">
         <v>18.5</v>
@@ -3741,28 +3741,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M30">
-        <v>4.1636476</v>
+        <v>4.312349300000001</v>
       </c>
       <c r="N30">
-        <v>17.81135239999999</v>
+        <v>17.66265069999999</v>
       </c>
       <c r="O30">
-        <v>4.452838099999998</v>
+        <v>4.415662674999998</v>
       </c>
       <c r="P30">
-        <v>13.3585143</v>
+        <v>13.24698802499999</v>
       </c>
       <c r="Q30">
-        <v>31.25851429999999</v>
+        <v>31.14698802499999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.137962097441374</v>
+        <v>0.1390089181756013</v>
       </c>
       <c r="T30">
-        <v>1.104078179436315</v>
+        <v>1.116618822092339</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.277824184736478</v>
+        <v>5.09583024733177</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1107240819046769</v>
+        <v>0.1105024536515646</v>
       </c>
       <c r="C31">
-        <v>215.9805811643328</v>
+        <v>214.2351322290541</v>
       </c>
       <c r="D31">
-        <v>275.4615811643328</v>
+        <v>276.4051322290541</v>
       </c>
       <c r="E31">
-        <v>-23.91900000000001</v>
+        <v>-21.23000000000002</v>
       </c>
       <c r="F31">
-        <v>77.98099999999999</v>
+        <v>80.66999999999999</v>
       </c>
       <c r="G31">
         <v>18.5</v>
@@ -3823,28 +3823,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M31">
-        <v>4.3123493</v>
+        <v>4.461050999999999</v>
       </c>
       <c r="N31">
-        <v>17.66265069999999</v>
+        <v>17.513949</v>
       </c>
       <c r="O31">
-        <v>4.415662674999998</v>
+        <v>4.378487249999999</v>
       </c>
       <c r="P31">
-        <v>13.24698802499999</v>
+        <v>13.13546175</v>
       </c>
       <c r="Q31">
-        <v>31.14698802499999</v>
+        <v>31.03546175</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1390089181756013</v>
+        <v>0.1400856480736637</v>
       </c>
       <c r="T31">
-        <v>1.116618822092339</v>
+        <v>1.129517768824249</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.095830247331771</v>
+        <v>4.925969239087381</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1105024536515646</v>
+        <v>0.1102808253984522</v>
       </c>
       <c r="C32">
-        <v>214.2351322290541</v>
+        <v>212.4961694878619</v>
       </c>
       <c r="D32">
-        <v>276.4051322290541</v>
+        <v>277.3551694878619</v>
       </c>
       <c r="E32">
-        <v>-21.23000000000002</v>
+        <v>-18.54100000000001</v>
       </c>
       <c r="F32">
-        <v>80.66999999999999</v>
+        <v>83.35899999999999</v>
       </c>
       <c r="G32">
         <v>18.5</v>
@@ -3905,28 +3905,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M32">
-        <v>4.461050999999999</v>
+        <v>4.6097527</v>
       </c>
       <c r="N32">
-        <v>17.513949</v>
+        <v>17.36524729999999</v>
       </c>
       <c r="O32">
-        <v>4.378487249999999</v>
+        <v>4.341311824999998</v>
       </c>
       <c r="P32">
-        <v>13.13546175</v>
+        <v>13.02393547499999</v>
       </c>
       <c r="Q32">
-        <v>31.03546175</v>
+        <v>30.92393547499999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1400856480736637</v>
+        <v>0.1411935875339888</v>
       </c>
       <c r="T32">
-        <v>1.129517768824249</v>
+        <v>1.142790598070127</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.925969239087381</v>
+        <v>4.767067005568432</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1102808253984522</v>
+        <v>0.1100591971453399</v>
       </c>
       <c r="C33">
-        <v>212.4961694878619</v>
+        <v>210.7637600528862</v>
       </c>
       <c r="D33">
-        <v>277.3551694878619</v>
+        <v>278.3117600528862</v>
       </c>
       <c r="E33">
-        <v>-18.54100000000001</v>
+        <v>-15.85200000000002</v>
       </c>
       <c r="F33">
-        <v>83.35899999999999</v>
+        <v>86.04799999999999</v>
       </c>
       <c r="G33">
         <v>18.5</v>
@@ -3987,28 +3987,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M33">
-        <v>4.6097527</v>
+        <v>4.7584544</v>
       </c>
       <c r="N33">
-        <v>17.36524729999999</v>
+        <v>17.2165456</v>
       </c>
       <c r="O33">
-        <v>4.341311824999998</v>
+        <v>4.304136399999999</v>
       </c>
       <c r="P33">
-        <v>13.02393547499999</v>
+        <v>12.9124092</v>
       </c>
       <c r="Q33">
-        <v>30.92393547499999</v>
+        <v>30.8124092</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1411935875339888</v>
+        <v>0.1423341134490293</v>
       </c>
       <c r="T33">
-        <v>1.142790598070127</v>
+        <v>1.156453804646767</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.767067005568432</v>
+        <v>4.618096161644419</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1100591971453399</v>
+        <v>0.1104563188922276</v>
       </c>
       <c r="C34">
-        <v>210.7637600528862</v>
+        <v>206.365357874952</v>
       </c>
       <c r="D34">
-        <v>278.3117600528862</v>
+        <v>276.602357874952</v>
       </c>
       <c r="E34">
-        <v>-15.85200000000002</v>
+        <v>-13.16300000000001</v>
       </c>
       <c r="F34">
-        <v>86.04799999999999</v>
+        <v>88.73699999999999</v>
       </c>
       <c r="G34">
         <v>18.5</v>
@@ -4069,45 +4069,45 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M34">
-        <v>4.7584544</v>
+        <v>5.1289986</v>
       </c>
       <c r="N34">
-        <v>17.2165456</v>
+        <v>16.8460014</v>
       </c>
       <c r="O34">
-        <v>4.304136399999999</v>
+        <v>4.211500349999999</v>
       </c>
       <c r="P34">
-        <v>12.9124092</v>
+        <v>12.63450105</v>
       </c>
       <c r="Q34">
-        <v>30.8124092</v>
+        <v>30.53450105</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1423341134490293</v>
+        <v>0.1435086849137725</v>
       </c>
       <c r="T34">
-        <v>1.156453804646767</v>
+        <v>1.170524868136142</v>
       </c>
       <c r="U34">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.618096161644419</v>
+        <v>4.28446207803605</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1104563188922276</v>
+        <v>0.1102534406391152</v>
       </c>
       <c r="C35">
-        <v>206.365357874952</v>
+        <v>204.5470112119341</v>
       </c>
       <c r="D35">
-        <v>276.602357874952</v>
+        <v>277.4730112119341</v>
       </c>
       <c r="E35">
-        <v>-13.16300000000001</v>
+        <v>-10.474</v>
       </c>
       <c r="F35">
-        <v>88.73699999999999</v>
+        <v>91.426</v>
       </c>
       <c r="G35">
         <v>18.5</v>
@@ -4151,28 +4151,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M35">
-        <v>5.1289986</v>
+        <v>5.284422800000001</v>
       </c>
       <c r="N35">
-        <v>16.8460014</v>
+        <v>16.69057719999999</v>
       </c>
       <c r="O35">
-        <v>4.211500349999999</v>
+        <v>4.172644299999998</v>
       </c>
       <c r="P35">
-        <v>12.63450105</v>
+        <v>12.51793289999999</v>
       </c>
       <c r="Q35">
-        <v>30.53450105</v>
+        <v>30.41793289999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1435086849137725</v>
+        <v>0.1447188494532049</v>
       </c>
       <c r="T35">
-        <v>1.170524868136142</v>
+        <v>1.185022327488831</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.28446207803605</v>
+        <v>4.158448487505578</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1102534406391152</v>
+        <v>0.1100505623860029</v>
       </c>
       <c r="C36">
-        <v>204.5470112119341</v>
+        <v>202.7341629172265</v>
       </c>
       <c r="D36">
-        <v>277.4730112119341</v>
+        <v>278.3491629172265</v>
       </c>
       <c r="E36">
-        <v>-10.474</v>
+        <v>-7.785000000000011</v>
       </c>
       <c r="F36">
-        <v>91.426</v>
+        <v>94.11499999999999</v>
       </c>
       <c r="G36">
         <v>18.5</v>
@@ -4233,28 +4233,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M36">
-        <v>5.284422800000001</v>
+        <v>5.439847</v>
       </c>
       <c r="N36">
-        <v>16.69057719999999</v>
+        <v>16.53515299999999</v>
       </c>
       <c r="O36">
-        <v>4.172644299999998</v>
+        <v>4.133788249999998</v>
       </c>
       <c r="P36">
-        <v>12.51793289999999</v>
+        <v>12.40136475</v>
       </c>
       <c r="Q36">
-        <v>30.41793289999999</v>
+        <v>30.30136474999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1447188494532049</v>
+        <v>0.1459662498246199</v>
       </c>
       <c r="T36">
-        <v>1.185022327488831</v>
+        <v>1.199965862513911</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.158448487505578</v>
+        <v>4.039635673576847</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1100505623860029</v>
+        <v>0.1107926841328906</v>
       </c>
       <c r="C37">
-        <v>202.7341629172265</v>
+        <v>196.8668210809903</v>
       </c>
       <c r="D37">
-        <v>278.3491629172265</v>
+        <v>275.1708210809903</v>
       </c>
       <c r="E37">
-        <v>-7.785000000000011</v>
+        <v>-5.096000000000004</v>
       </c>
       <c r="F37">
-        <v>94.11499999999999</v>
+        <v>96.804</v>
       </c>
       <c r="G37">
         <v>18.5</v>
@@ -4315,45 +4315,45 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M37">
-        <v>5.439847</v>
+        <v>5.9340852</v>
       </c>
       <c r="N37">
-        <v>16.53515299999999</v>
+        <v>16.0409148</v>
       </c>
       <c r="O37">
-        <v>4.133788249999998</v>
+        <v>4.010228699999999</v>
       </c>
       <c r="P37">
-        <v>12.40136475</v>
+        <v>12.0306861</v>
       </c>
       <c r="Q37">
-        <v>30.30136474999999</v>
+        <v>29.9306861</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1459662498246199</v>
+        <v>0.1472526314576415</v>
       </c>
       <c r="T37">
-        <v>1.199965862513911</v>
+        <v>1.215376383008524</v>
       </c>
       <c r="U37">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.039635673576847</v>
+        <v>3.703182421445515</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1107926841328906</v>
+        <v>0.1106160558797782</v>
       </c>
       <c r="C38">
-        <v>196.8668210809903</v>
+        <v>194.9276806763532</v>
       </c>
       <c r="D38">
-        <v>275.1708210809903</v>
+        <v>275.9206806763532</v>
       </c>
       <c r="E38">
-        <v>-5.096000000000018</v>
+        <v>-2.407000000000011</v>
       </c>
       <c r="F38">
-        <v>96.80399999999999</v>
+        <v>99.49299999999999</v>
       </c>
       <c r="G38">
         <v>18.5</v>
@@ -4397,28 +4397,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M38">
-        <v>5.934085199999999</v>
+        <v>6.0989209</v>
       </c>
       <c r="N38">
-        <v>16.0409148</v>
+        <v>15.87607909999999</v>
       </c>
       <c r="O38">
-        <v>4.010228699999999</v>
+        <v>3.969019774999999</v>
       </c>
       <c r="P38">
-        <v>12.0306861</v>
+        <v>11.907059325</v>
       </c>
       <c r="Q38">
-        <v>29.9306861</v>
+        <v>29.80705932499999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1472526314576415</v>
+        <v>0.1485798506028226</v>
       </c>
       <c r="T38">
-        <v>1.215376383008524</v>
+        <v>1.231276126375983</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.703182421445516</v>
+        <v>3.603096410055096</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1106160558797782</v>
+        <v>0.1104394276266659</v>
       </c>
       <c r="C39">
-        <v>194.9276806763532</v>
+        <v>192.9926382780032</v>
       </c>
       <c r="D39">
-        <v>275.9206806763532</v>
+        <v>276.6746382780032</v>
       </c>
       <c r="E39">
-        <v>-2.407000000000011</v>
+        <v>0.2819999999999823</v>
       </c>
       <c r="F39">
-        <v>99.49299999999999</v>
+        <v>102.182</v>
       </c>
       <c r="G39">
         <v>18.5</v>
@@ -4479,28 +4479,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M39">
-        <v>6.0989209</v>
+        <v>6.263756599999999</v>
       </c>
       <c r="N39">
-        <v>15.87607909999999</v>
+        <v>15.7112434</v>
       </c>
       <c r="O39">
-        <v>3.969019774999999</v>
+        <v>3.927810849999999</v>
       </c>
       <c r="P39">
-        <v>11.907059325</v>
+        <v>11.78343255</v>
       </c>
       <c r="Q39">
-        <v>29.80705932499999</v>
+        <v>29.68343255</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1485798506028226</v>
+        <v>0.1499498832688159</v>
       </c>
       <c r="T39">
-        <v>1.231276126375983</v>
+        <v>1.247688764690778</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.603096410055096</v>
+        <v>3.508278083474699</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1104394276266659</v>
+        <v>0.1110817993735536</v>
       </c>
       <c r="C40">
-        <v>192.9926382780032</v>
+        <v>187.5811647491538</v>
       </c>
       <c r="D40">
-        <v>276.6746382780032</v>
+        <v>273.9521647491538</v>
       </c>
       <c r="E40">
-        <v>0.2819999999999823</v>
+        <v>2.970999999999989</v>
       </c>
       <c r="F40">
-        <v>102.182</v>
+        <v>104.871</v>
       </c>
       <c r="G40">
         <v>18.5</v>
@@ -4561,45 +4561,45 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M40">
-        <v>6.263756599999999</v>
+        <v>6.7222311</v>
       </c>
       <c r="N40">
-        <v>15.7112434</v>
+        <v>15.25276889999999</v>
       </c>
       <c r="O40">
-        <v>3.927810849999999</v>
+        <v>3.813192224999999</v>
       </c>
       <c r="P40">
-        <v>11.78343255</v>
+        <v>11.439576675</v>
       </c>
       <c r="Q40">
-        <v>29.68343255</v>
+        <v>29.339576675</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1499498832688159</v>
+        <v>0.1513648350386124</v>
       </c>
       <c r="T40">
-        <v>1.247688764690778</v>
+        <v>1.264639522294584</v>
       </c>
       <c r="U40">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.508278083474699</v>
+        <v>3.269003947216274</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1110817993735536</v>
+        <v>0.1109261711204412</v>
       </c>
       <c r="C41">
-        <v>187.5811647491538</v>
+        <v>185.5468124292302</v>
       </c>
       <c r="D41">
-        <v>273.9521647491538</v>
+        <v>274.6068124292302</v>
       </c>
       <c r="E41">
-        <v>2.970999999999989</v>
+        <v>5.659999999999997</v>
       </c>
       <c r="F41">
-        <v>104.871</v>
+        <v>107.56</v>
       </c>
       <c r="G41">
         <v>18.5</v>
@@ -4643,28 +4643,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M41">
-        <v>6.7222311</v>
+        <v>6.894596000000001</v>
       </c>
       <c r="N41">
-        <v>15.25276889999999</v>
+        <v>15.08040399999999</v>
       </c>
       <c r="O41">
-        <v>3.813192224999999</v>
+        <v>3.770100999999999</v>
       </c>
       <c r="P41">
-        <v>11.439576675</v>
+        <v>11.310303</v>
       </c>
       <c r="Q41">
-        <v>29.339576675</v>
+        <v>29.210303</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1513648350386124</v>
+        <v>0.152826951867402</v>
       </c>
       <c r="T41">
-        <v>1.264639522294584</v>
+        <v>1.28215530515185</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.269003947216274</v>
+        <v>3.187278848535867</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1109261711204412</v>
+        <v>0.1107705428673289</v>
       </c>
       <c r="C42">
-        <v>185.5468124292302</v>
+        <v>183.5155963513743</v>
       </c>
       <c r="D42">
-        <v>274.6068124292302</v>
+        <v>275.2645963513743</v>
       </c>
       <c r="E42">
-        <v>5.659999999999997</v>
+        <v>8.34899999999999</v>
       </c>
       <c r="F42">
-        <v>107.56</v>
+        <v>110.249</v>
       </c>
       <c r="G42">
         <v>18.5</v>
@@ -4725,28 +4725,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M42">
-        <v>6.894596000000001</v>
+        <v>7.0669609</v>
       </c>
       <c r="N42">
-        <v>15.08040399999999</v>
+        <v>14.90803909999999</v>
       </c>
       <c r="O42">
-        <v>3.770100999999999</v>
+        <v>3.727009774999999</v>
       </c>
       <c r="P42">
-        <v>11.310303</v>
+        <v>11.181029325</v>
       </c>
       <c r="Q42">
-        <v>29.210303</v>
+        <v>29.081029325</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.152826951867402</v>
+        <v>0.1543386319785235</v>
       </c>
       <c r="T42">
-        <v>1.28215530515185</v>
+        <v>1.300264843360209</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.187278848535867</v>
+        <v>3.109540340034992</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1107705428673289</v>
+        <v>0.1106149146142165</v>
       </c>
       <c r="C43">
-        <v>183.5155963513743</v>
+        <v>181.4875391070475</v>
       </c>
       <c r="D43">
-        <v>275.2645963513743</v>
+        <v>275.9255391070475</v>
       </c>
       <c r="E43">
-        <v>8.34899999999999</v>
+        <v>11.038</v>
       </c>
       <c r="F43">
-        <v>110.249</v>
+        <v>112.938</v>
       </c>
       <c r="G43">
         <v>18.5</v>
@@ -4807,28 +4807,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M43">
-        <v>7.0669609</v>
+        <v>7.2393258</v>
       </c>
       <c r="N43">
-        <v>14.90803909999999</v>
+        <v>14.73567419999999</v>
       </c>
       <c r="O43">
-        <v>3.727009774999999</v>
+        <v>3.683918549999999</v>
       </c>
       <c r="P43">
-        <v>11.181029325</v>
+        <v>11.05175565</v>
       </c>
       <c r="Q43">
-        <v>29.081029325</v>
+        <v>28.95175565</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1543386319785235</v>
+        <v>0.1559024389900285</v>
       </c>
       <c r="T43">
-        <v>1.300264843360209</v>
+        <v>1.31899884840334</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.109540340034992</v>
+        <v>3.035503665272254</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1106149146142166</v>
+        <v>0.1129747863611042</v>
       </c>
       <c r="C44">
-        <v>181.4875391070474</v>
+        <v>169.1051865970273</v>
       </c>
       <c r="D44">
-        <v>275.9255391070474</v>
+        <v>266.2321865970274</v>
       </c>
       <c r="E44">
-        <v>11.03799999999998</v>
+        <v>13.72699999999999</v>
       </c>
       <c r="F44">
-        <v>112.938</v>
+        <v>115.627</v>
       </c>
       <c r="G44">
         <v>18.5</v>
@@ -4889,45 +4889,45 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M44">
-        <v>7.2393258</v>
+        <v>8.313581300000001</v>
       </c>
       <c r="N44">
-        <v>14.73567419999999</v>
+        <v>13.66141869999999</v>
       </c>
       <c r="O44">
-        <v>3.683918549999999</v>
+        <v>3.415354674999998</v>
       </c>
       <c r="P44">
-        <v>11.05175565</v>
+        <v>10.246064025</v>
       </c>
       <c r="Q44">
-        <v>28.95175565</v>
+        <v>28.14606402499999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1559024389900285</v>
+        <v>0.1575211164229898</v>
       </c>
       <c r="T44">
-        <v>1.31899884840334</v>
+        <v>1.338390186956755</v>
       </c>
       <c r="U44">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.035503665272254</v>
+        <v>2.64326518344146</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1129747863611042</v>
+        <v>0.1128776581079919</v>
       </c>
       <c r="C45">
-        <v>169.1051865970273</v>
+        <v>166.8016900259756</v>
       </c>
       <c r="D45">
-        <v>266.2321865970274</v>
+        <v>266.6176900259756</v>
       </c>
       <c r="E45">
-        <v>13.72699999999999</v>
+        <v>16.41599999999998</v>
       </c>
       <c r="F45">
-        <v>115.627</v>
+        <v>118.316</v>
       </c>
       <c r="G45">
         <v>18.5</v>
@@ -4971,28 +4971,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M45">
-        <v>8.313581300000001</v>
+        <v>8.5069204</v>
       </c>
       <c r="N45">
-        <v>13.66141869999999</v>
+        <v>13.46807959999999</v>
       </c>
       <c r="O45">
-        <v>3.415354674999998</v>
+        <v>3.367019899999999</v>
       </c>
       <c r="P45">
-        <v>10.246064025</v>
+        <v>10.1010597</v>
       </c>
       <c r="Q45">
-        <v>28.14606402499999</v>
+        <v>28.00105969999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1575211164229898</v>
+        <v>0.1591976037642712</v>
       </c>
       <c r="T45">
-        <v>1.338390186956755</v>
+        <v>1.35847407331565</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.64326518344146</v>
+        <v>2.583190974726882</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1128776581079919</v>
+        <v>0.1127805298548795</v>
       </c>
       <c r="C46">
-        <v>166.8016900259756</v>
+        <v>164.499311489514</v>
       </c>
       <c r="D46">
-        <v>266.6176900259756</v>
+        <v>267.004311489514</v>
       </c>
       <c r="E46">
-        <v>16.41599999999998</v>
+        <v>19.10499999999999</v>
       </c>
       <c r="F46">
-        <v>118.316</v>
+        <v>121.005</v>
       </c>
       <c r="G46">
         <v>18.5</v>
@@ -5053,28 +5053,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M46">
-        <v>8.5069204</v>
+        <v>8.7002595</v>
       </c>
       <c r="N46">
-        <v>13.46807959999999</v>
+        <v>13.27474049999999</v>
       </c>
       <c r="O46">
-        <v>3.367019899999999</v>
+        <v>3.318685124999999</v>
       </c>
       <c r="P46">
-        <v>10.1010597</v>
+        <v>9.956055374999996</v>
       </c>
       <c r="Q46">
-        <v>28.00105969999999</v>
+        <v>27.856055375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1591976037642712</v>
+        <v>0.1609350542815992</v>
       </c>
       <c r="T46">
-        <v>1.35847407331565</v>
+        <v>1.379288282814868</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.583190974726882</v>
+        <v>2.525786730844062</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1127805298548795</v>
+        <v>0.1140289016017672</v>
       </c>
       <c r="C47">
-        <v>164.499311489514</v>
+        <v>156.9249823850504</v>
       </c>
       <c r="D47">
-        <v>267.004311489514</v>
+        <v>262.1189823850503</v>
       </c>
       <c r="E47">
-        <v>19.10499999999999</v>
+        <v>21.79399999999998</v>
       </c>
       <c r="F47">
-        <v>121.005</v>
+        <v>123.694</v>
       </c>
       <c r="G47">
         <v>18.5</v>
@@ -5135,45 +5135,45 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M47">
-        <v>8.7002595</v>
+        <v>9.3760052</v>
       </c>
       <c r="N47">
-        <v>13.27474049999999</v>
+        <v>12.59899479999999</v>
       </c>
       <c r="O47">
-        <v>3.318685124999999</v>
+        <v>3.149748699999999</v>
       </c>
       <c r="P47">
-        <v>9.956055374999996</v>
+        <v>9.449246099999996</v>
       </c>
       <c r="Q47">
-        <v>27.856055375</v>
+        <v>27.34924609999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1609350542815992</v>
+        <v>0.1627368548180874</v>
       </c>
       <c r="T47">
-        <v>1.379288282814868</v>
+        <v>1.400873388962206</v>
       </c>
       <c r="U47">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.525786730844062</v>
+        <v>2.343748700139372</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1140289016017672</v>
+        <v>0.1139610233486549</v>
       </c>
       <c r="C48">
-        <v>156.9249823850504</v>
+        <v>154.4970139505664</v>
       </c>
       <c r="D48">
-        <v>262.1189823850503</v>
+        <v>262.3800139505664</v>
       </c>
       <c r="E48">
-        <v>21.79399999999998</v>
+        <v>24.48299999999999</v>
       </c>
       <c r="F48">
-        <v>123.694</v>
+        <v>126.383</v>
       </c>
       <c r="G48">
         <v>18.5</v>
@@ -5217,28 +5217,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M48">
-        <v>9.3760052</v>
+        <v>9.5798314</v>
       </c>
       <c r="N48">
-        <v>12.59899479999999</v>
+        <v>12.39516859999999</v>
       </c>
       <c r="O48">
-        <v>3.149748699999999</v>
+        <v>3.098792149999999</v>
       </c>
       <c r="P48">
-        <v>9.449246099999996</v>
+        <v>9.296376449999997</v>
       </c>
       <c r="Q48">
-        <v>27.34924609999999</v>
+        <v>27.19637645</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1627368548180874</v>
+        <v>0.1646066478276507</v>
       </c>
       <c r="T48">
-        <v>1.400873388962206</v>
+        <v>1.42327302741699</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.343748700139372</v>
+        <v>2.293881706519385</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1139610233486549</v>
+        <v>0.1138931450955425</v>
       </c>
       <c r="C49">
-        <v>154.4970139505664</v>
+        <v>152.0695659316588</v>
       </c>
       <c r="D49">
-        <v>262.3800139505664</v>
+        <v>262.6415659316588</v>
       </c>
       <c r="E49">
-        <v>24.48299999999999</v>
+        <v>27.172</v>
       </c>
       <c r="F49">
-        <v>126.383</v>
+        <v>129.072</v>
       </c>
       <c r="G49">
         <v>18.5</v>
@@ -5299,28 +5299,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M49">
-        <v>9.5798314</v>
+        <v>9.783657600000002</v>
       </c>
       <c r="N49">
-        <v>12.39516859999999</v>
+        <v>12.19134239999999</v>
       </c>
       <c r="O49">
-        <v>3.098792149999999</v>
+        <v>3.047835599999998</v>
       </c>
       <c r="P49">
-        <v>9.296376449999997</v>
+        <v>9.143506799999994</v>
       </c>
       <c r="Q49">
-        <v>27.19637645</v>
+        <v>27.04350679999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1646066478276507</v>
+        <v>0.1665483559529664</v>
       </c>
       <c r="T49">
-        <v>1.42327302741699</v>
+        <v>1.446534190427728</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.293881706519385</v>
+        <v>2.246092504300231</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1138931450955425</v>
+        <v>0.1138252668424302</v>
       </c>
       <c r="C50">
-        <v>152.0695659316588</v>
+        <v>149.6426398862003</v>
       </c>
       <c r="D50">
-        <v>262.6415659316588</v>
+        <v>262.9036398862003</v>
       </c>
       <c r="E50">
-        <v>27.17199999999997</v>
+        <v>29.86099999999999</v>
       </c>
       <c r="F50">
-        <v>129.072</v>
+        <v>131.761</v>
       </c>
       <c r="G50">
         <v>18.5</v>
@@ -5381,28 +5381,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M50">
-        <v>9.7836576</v>
+        <v>9.9874838</v>
       </c>
       <c r="N50">
-        <v>12.19134239999999</v>
+        <v>11.98751619999999</v>
       </c>
       <c r="O50">
-        <v>3.047835599999999</v>
+        <v>2.996879049999999</v>
       </c>
       <c r="P50">
-        <v>9.143506799999995</v>
+        <v>8.990637149999996</v>
       </c>
       <c r="Q50">
-        <v>27.0435068</v>
+        <v>26.89063715</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1665483559529664</v>
+        <v>0.1685662094949612</v>
       </c>
       <c r="T50">
-        <v>1.446534190427728</v>
+        <v>1.470707555909474</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.246092504300232</v>
+        <v>2.200253881763492</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1138252668424302</v>
+        <v>0.1137573885893179</v>
       </c>
       <c r="C51">
-        <v>149.6426398862003</v>
+        <v>147.2162373782875</v>
       </c>
       <c r="D51">
-        <v>262.9036398862003</v>
+        <v>263.1662373782875</v>
       </c>
       <c r="E51">
-        <v>29.86099999999999</v>
+        <v>32.54999999999998</v>
       </c>
       <c r="F51">
-        <v>131.761</v>
+        <v>134.45</v>
       </c>
       <c r="G51">
         <v>18.5</v>
@@ -5463,28 +5463,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M51">
-        <v>9.9874838</v>
+        <v>10.19131</v>
       </c>
       <c r="N51">
-        <v>11.98751619999999</v>
+        <v>11.78368999999999</v>
       </c>
       <c r="O51">
-        <v>2.996879049999999</v>
+        <v>2.945922499999999</v>
       </c>
       <c r="P51">
-        <v>8.990637149999996</v>
+        <v>8.837767499999996</v>
       </c>
       <c r="Q51">
-        <v>26.89063715</v>
+        <v>26.7377675</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1685662094949612</v>
+        <v>0.1706647771786357</v>
       </c>
       <c r="T51">
-        <v>1.470707555909474</v>
+        <v>1.495847856010491</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.200253881763492</v>
+        <v>2.156248804128222</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1137573885893179</v>
+        <v>0.1136895103362055</v>
       </c>
       <c r="C52">
-        <v>147.2162373782875</v>
+        <v>144.7903599782728</v>
       </c>
       <c r="D52">
-        <v>263.1662373782875</v>
+        <v>263.4293599782728</v>
       </c>
       <c r="E52">
-        <v>32.54999999999998</v>
+        <v>35.23899999999998</v>
       </c>
       <c r="F52">
-        <v>134.45</v>
+        <v>137.139</v>
       </c>
       <c r="G52">
         <v>18.5</v>
@@ -5545,28 +5545,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M52">
-        <v>10.19131</v>
+        <v>10.3951362</v>
       </c>
       <c r="N52">
-        <v>11.78368999999999</v>
+        <v>11.57986379999999</v>
       </c>
       <c r="O52">
-        <v>2.945922499999999</v>
+        <v>2.894965949999999</v>
       </c>
       <c r="P52">
-        <v>8.837767499999996</v>
+        <v>8.684897849999995</v>
       </c>
       <c r="Q52">
-        <v>26.7377675</v>
+        <v>26.58489784999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1706647771786357</v>
+        <v>0.1728490006861337</v>
       </c>
       <c r="T52">
-        <v>1.495847856010491</v>
+        <v>1.522014290809509</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.156248804128222</v>
+        <v>2.113969415811983</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1136895103362055</v>
+        <v>0.1136216320830932</v>
       </c>
       <c r="C53">
-        <v>144.7903599782728</v>
+        <v>142.3650092627948</v>
       </c>
       <c r="D53">
-        <v>263.4293599782728</v>
+        <v>263.6930092627948</v>
       </c>
       <c r="E53">
-        <v>35.23899999999998</v>
+        <v>37.928</v>
       </c>
       <c r="F53">
-        <v>137.139</v>
+        <v>139.828</v>
       </c>
       <c r="G53">
         <v>18.5</v>
@@ -5627,28 +5627,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M53">
-        <v>10.3951362</v>
+        <v>10.5989624</v>
       </c>
       <c r="N53">
-        <v>11.57986379999999</v>
+        <v>11.37603759999999</v>
       </c>
       <c r="O53">
-        <v>2.894965949999999</v>
+        <v>2.844009399999998</v>
       </c>
       <c r="P53">
-        <v>8.684897849999995</v>
+        <v>8.532028199999996</v>
       </c>
       <c r="Q53">
-        <v>26.58489784999999</v>
+        <v>26.43202819999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1728490006861337</v>
+        <v>0.1751242335064441</v>
       </c>
       <c r="T53">
-        <v>1.522014290809509</v>
+        <v>1.549270993725152</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.113969415811983</v>
+        <v>2.073316157815598</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1136216320830932</v>
+        <v>0.1135537538299809</v>
       </c>
       <c r="C54">
-        <v>142.3650092627948</v>
+        <v>139.9401868148107</v>
       </c>
       <c r="D54">
-        <v>263.6930092627948</v>
+        <v>263.9571868148107</v>
       </c>
       <c r="E54">
-        <v>37.928</v>
+        <v>40.61699999999999</v>
       </c>
       <c r="F54">
-        <v>139.828</v>
+        <v>142.517</v>
       </c>
       <c r="G54">
         <v>18.5</v>
@@ -5709,28 +5709,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M54">
-        <v>10.5989624</v>
+        <v>10.8027886</v>
       </c>
       <c r="N54">
-        <v>11.37603759999999</v>
+        <v>11.17221139999999</v>
       </c>
       <c r="O54">
-        <v>2.844009399999998</v>
+        <v>2.793052849999998</v>
       </c>
       <c r="P54">
-        <v>8.532028199999996</v>
+        <v>8.379158549999994</v>
       </c>
       <c r="Q54">
-        <v>26.43202819999999</v>
+        <v>26.27915854999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1751242335064441</v>
+        <v>0.1774962847446401</v>
       </c>
       <c r="T54">
-        <v>1.549270993725152</v>
+        <v>1.577687556339333</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.073316157815598</v>
+        <v>2.034196985026624</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1135537538299809</v>
+        <v>0.1192368755768685</v>
       </c>
       <c r="C55">
-        <v>139.9401868148107</v>
+        <v>116.8241082272373</v>
       </c>
       <c r="D55">
-        <v>263.9571868148107</v>
+        <v>243.5301082272373</v>
       </c>
       <c r="E55">
-        <v>40.61699999999999</v>
+        <v>43.30599999999998</v>
       </c>
       <c r="F55">
-        <v>142.517</v>
+        <v>145.206</v>
       </c>
       <c r="G55">
         <v>18.5</v>
@@ -5791,45 +5791,45 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M55">
-        <v>10.8027886</v>
+        <v>13.06854</v>
       </c>
       <c r="N55">
-        <v>11.17221139999999</v>
+        <v>8.906459999999996</v>
       </c>
       <c r="O55">
-        <v>2.793052849999998</v>
+        <v>2.226614999999999</v>
       </c>
       <c r="P55">
-        <v>8.379158549999994</v>
+        <v>6.679844999999997</v>
       </c>
       <c r="Q55">
-        <v>26.27915854999999</v>
+        <v>24.579845</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1774962847446401</v>
+        <v>0.1799714686453663</v>
       </c>
       <c r="T55">
-        <v>1.577687556339333</v>
+        <v>1.60733962167587</v>
       </c>
       <c r="U55">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.034196985026624</v>
+        <v>1.68151912914526</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1192368755768685</v>
+        <v>0.1192754973237562</v>
       </c>
       <c r="C56">
-        <v>116.8241082272373</v>
+        <v>114.0070987745345</v>
       </c>
       <c r="D56">
-        <v>243.5301082272373</v>
+        <v>243.4020987745345</v>
       </c>
       <c r="E56">
-        <v>43.30599999999998</v>
+        <v>45.995</v>
       </c>
       <c r="F56">
-        <v>145.206</v>
+        <v>147.895</v>
       </c>
       <c r="G56">
         <v>18.5</v>
@@ -5873,28 +5873,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M56">
-        <v>13.06854</v>
+        <v>13.31055</v>
       </c>
       <c r="N56">
-        <v>8.906459999999996</v>
+        <v>8.664449999999993</v>
       </c>
       <c r="O56">
-        <v>2.226614999999999</v>
+        <v>2.166112499999998</v>
       </c>
       <c r="P56">
-        <v>6.679844999999997</v>
+        <v>6.498337499999995</v>
       </c>
       <c r="Q56">
-        <v>24.579845</v>
+        <v>24.39833749999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1799714686453663</v>
+        <v>0.1825566607194582</v>
       </c>
       <c r="T56">
-        <v>1.60733962167587</v>
+        <v>1.638309556582919</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.68151912914526</v>
+        <v>1.650946054069891</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1192754973237562</v>
+        <v>0.1193141190706438</v>
       </c>
       <c r="C57">
-        <v>114.0070987745345</v>
+        <v>111.1902238252101</v>
       </c>
       <c r="D57">
-        <v>243.4020987745345</v>
+        <v>243.2742238252101</v>
       </c>
       <c r="E57">
-        <v>45.995</v>
+        <v>48.684</v>
       </c>
       <c r="F57">
-        <v>147.895</v>
+        <v>150.584</v>
       </c>
       <c r="G57">
         <v>18.5</v>
@@ -5955,28 +5955,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M57">
-        <v>13.31055</v>
+        <v>13.55256</v>
       </c>
       <c r="N57">
-        <v>8.664449999999993</v>
+        <v>8.422439999999995</v>
       </c>
       <c r="O57">
-        <v>2.166112499999998</v>
+        <v>2.105609999999999</v>
       </c>
       <c r="P57">
-        <v>6.498337499999995</v>
+        <v>6.316829999999996</v>
       </c>
       <c r="Q57">
-        <v>24.39833749999999</v>
+        <v>24.21682999999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1825566607194582</v>
+        <v>0.1852593615241905</v>
       </c>
       <c r="T57">
-        <v>1.638309556582919</v>
+        <v>1.670687215803925</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.650946054069891</v>
+        <v>1.621464874532929</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1193141190706438</v>
+        <v>0.1193527408175315</v>
       </c>
       <c r="C58">
-        <v>111.1902238252101</v>
+        <v>108.373483167385</v>
       </c>
       <c r="D58">
-        <v>243.2742238252101</v>
+        <v>243.146483167385</v>
       </c>
       <c r="E58">
-        <v>48.684</v>
+        <v>51.37299999999999</v>
       </c>
       <c r="F58">
-        <v>150.584</v>
+        <v>153.273</v>
       </c>
       <c r="G58">
         <v>18.5</v>
@@ -6037,28 +6037,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M58">
-        <v>13.55256</v>
+        <v>13.79457</v>
       </c>
       <c r="N58">
-        <v>8.422439999999995</v>
+        <v>8.180429999999996</v>
       </c>
       <c r="O58">
-        <v>2.105609999999999</v>
+        <v>2.045107499999999</v>
       </c>
       <c r="P58">
-        <v>6.316829999999996</v>
+        <v>6.135322499999997</v>
       </c>
       <c r="Q58">
-        <v>24.21682999999999</v>
+        <v>24.0353225</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1852593615241905</v>
+        <v>0.1880877693430965</v>
       </c>
       <c r="T58">
-        <v>1.670687215803925</v>
+        <v>1.704570812663118</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.621464874532929</v>
+        <v>1.593018122348141</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1193527408175315</v>
+        <v>0.1193913625644192</v>
       </c>
       <c r="C59">
-        <v>108.373483167385</v>
+        <v>105.5568765896253</v>
       </c>
       <c r="D59">
-        <v>243.146483167385</v>
+        <v>243.0188765896253</v>
       </c>
       <c r="E59">
-        <v>51.37299999999999</v>
+        <v>54.06200000000001</v>
       </c>
       <c r="F59">
-        <v>153.273</v>
+        <v>155.962</v>
       </c>
       <c r="G59">
         <v>18.5</v>
@@ -6119,28 +6119,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M59">
-        <v>13.79457</v>
+        <v>14.03658</v>
       </c>
       <c r="N59">
-        <v>8.180429999999996</v>
+        <v>7.938419999999994</v>
       </c>
       <c r="O59">
-        <v>2.045107499999999</v>
+        <v>1.984604999999998</v>
       </c>
       <c r="P59">
-        <v>6.135322499999997</v>
+        <v>5.953814999999995</v>
       </c>
       <c r="Q59">
-        <v>24.0353225</v>
+        <v>23.85381499999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1880877693430965</v>
+        <v>0.1910508632486171</v>
       </c>
       <c r="T59">
-        <v>1.704570812663118</v>
+        <v>1.740067914134653</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.593018122348141</v>
+        <v>1.565552292652483</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1193913625644192</v>
+        <v>0.1194299843113068</v>
       </c>
       <c r="C60">
-        <v>105.5568765896252</v>
+        <v>102.7404038809407</v>
       </c>
       <c r="D60">
-        <v>243.0188765896252</v>
+        <v>242.8914038809407</v>
       </c>
       <c r="E60">
-        <v>54.06199999999998</v>
+        <v>56.75099999999998</v>
       </c>
       <c r="F60">
-        <v>155.962</v>
+        <v>158.651</v>
       </c>
       <c r="G60">
         <v>18.5</v>
@@ -6201,28 +6201,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M60">
-        <v>14.03658</v>
+        <v>14.27859</v>
       </c>
       <c r="N60">
-        <v>7.938419999999995</v>
+        <v>7.696409999999997</v>
       </c>
       <c r="O60">
-        <v>1.984604999999999</v>
+        <v>1.924102499999999</v>
       </c>
       <c r="P60">
-        <v>5.953814999999997</v>
+        <v>5.772307499999997</v>
       </c>
       <c r="Q60">
-        <v>23.853815</v>
+        <v>23.6723075</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1910508632486171</v>
+        <v>0.1941584983202605</v>
       </c>
       <c r="T60">
-        <v>1.740067914134653</v>
+        <v>1.777296581531629</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.565552292652483</v>
+        <v>1.539017508031255</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1194299843113068</v>
+        <v>0.1194686060581945</v>
       </c>
       <c r="C61">
-        <v>102.7404038809407</v>
+        <v>99.9240648307831</v>
       </c>
       <c r="D61">
-        <v>242.8914038809407</v>
+        <v>242.7640648307831</v>
       </c>
       <c r="E61">
-        <v>56.75099999999998</v>
+        <v>59.43999999999997</v>
       </c>
       <c r="F61">
-        <v>158.651</v>
+        <v>161.34</v>
       </c>
       <c r="G61">
         <v>18.5</v>
@@ -6283,28 +6283,28 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M61">
-        <v>14.27859</v>
+        <v>14.5206</v>
       </c>
       <c r="N61">
-        <v>7.696409999999997</v>
+        <v>7.454399999999998</v>
       </c>
       <c r="O61">
-        <v>1.924102499999999</v>
+        <v>1.863599999999999</v>
       </c>
       <c r="P61">
-        <v>5.772307499999997</v>
+        <v>5.590799999999998</v>
       </c>
       <c r="Q61">
-        <v>23.6723075</v>
+        <v>23.4908</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1941584983202605</v>
+        <v>0.1974215151454862</v>
       </c>
       <c r="T61">
-        <v>1.777296581531629</v>
+        <v>1.816386682298454</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.539017508031255</v>
+        <v>1.513367216230734</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1194686060581945</v>
+        <v>0.1484007367285236</v>
       </c>
       <c r="C62">
-        <v>99.9240648307831</v>
+        <v>28.77862027007032</v>
       </c>
       <c r="D62">
-        <v>242.7640648307831</v>
+        <v>174.3076202700703</v>
       </c>
       <c r="E62">
-        <v>59.43999999999997</v>
+        <v>62.12899999999999</v>
       </c>
       <c r="F62">
-        <v>161.34</v>
+        <v>164.029</v>
       </c>
       <c r="G62">
         <v>18.5</v>
@@ -6365,45 +6365,45 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M62">
-        <v>14.5206</v>
+        <v>24.0794572</v>
       </c>
       <c r="N62">
-        <v>7.454399999999998</v>
+        <v>-2.104457200000006</v>
       </c>
       <c r="O62">
-        <v>1.863599999999999</v>
+        <v>-0.5261143000000015</v>
       </c>
       <c r="P62">
-        <v>5.590799999999998</v>
+        <v>-1.578342900000004</v>
       </c>
       <c r="Q62">
-        <v>23.4908</v>
+        <v>16.3216571</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1974215151454862</v>
+        <v>0.2032902414042013</v>
       </c>
       <c r="T62">
-        <v>1.816386682298454</v>
+        <v>1.886692510651091</v>
       </c>
       <c r="U62">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.25</v>
+        <v>0.228150906989714</v>
       </c>
       <c r="W62">
-        <v>0.0675</v>
+        <v>0.11330744685391</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.513367216230734</v>
+        <v>0.9126036279588559</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1484007367285236</v>
+        <v>0.1494107367285236</v>
       </c>
       <c r="C63">
-        <v>28.77862027007032</v>
+        <v>24.3904653172969</v>
       </c>
       <c r="D63">
-        <v>174.3076202700703</v>
+        <v>172.6084653172969</v>
       </c>
       <c r="E63">
-        <v>62.12899999999999</v>
+        <v>64.81799999999998</v>
       </c>
       <c r="F63">
-        <v>164.029</v>
+        <v>166.718</v>
       </c>
       <c r="G63">
         <v>18.5</v>
@@ -6447,37 +6447,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M63">
-        <v>24.0794572</v>
+        <v>24.4742024</v>
       </c>
       <c r="N63">
-        <v>-2.104457200000006</v>
+        <v>-2.499202400000005</v>
       </c>
       <c r="O63">
-        <v>-0.5261143000000015</v>
+        <v>-0.6248006000000013</v>
       </c>
       <c r="P63">
-        <v>-1.578342900000004</v>
+        <v>-1.874401800000004</v>
       </c>
       <c r="Q63">
-        <v>16.3216571</v>
+        <v>16.02559819999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2032902414042013</v>
+        <v>0.207434721441154</v>
       </c>
       <c r="T63">
-        <v>1.886692510651091</v>
+        <v>1.936342313562962</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.228150906989714</v>
+        <v>0.2244710536511702</v>
       </c>
       <c r="W63">
-        <v>0.11330744685391</v>
+        <v>0.1138476493240082</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.9126036279588559</v>
+        <v>0.8978842146046808</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1494107367285236</v>
+        <v>0.1504207367285236</v>
       </c>
       <c r="C64">
-        <v>24.3904653172969</v>
+        <v>20.0351173692525</v>
       </c>
       <c r="D64">
-        <v>172.6084653172969</v>
+        <v>170.9421173692525</v>
       </c>
       <c r="E64">
-        <v>64.81799999999998</v>
+        <v>67.50699999999998</v>
       </c>
       <c r="F64">
-        <v>166.718</v>
+        <v>169.407</v>
       </c>
       <c r="G64">
         <v>18.5</v>
@@ -6529,37 +6529,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M64">
-        <v>24.4742024</v>
+        <v>24.8689476</v>
       </c>
       <c r="N64">
-        <v>-2.499202400000005</v>
+        <v>-2.893947600000004</v>
       </c>
       <c r="O64">
-        <v>-0.6248006000000013</v>
+        <v>-0.723486900000001</v>
       </c>
       <c r="P64">
-        <v>-1.874401800000004</v>
+        <v>-2.170460700000003</v>
       </c>
       <c r="Q64">
-        <v>16.02559819999999</v>
+        <v>15.7295393</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.207434721441154</v>
+        <v>0.21180322742605</v>
       </c>
       <c r="T64">
-        <v>1.936342313562962</v>
+        <v>1.988675889605204</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2244710536511702</v>
+        <v>0.2209080210535326</v>
       </c>
       <c r="W64">
-        <v>0.1138476493240082</v>
+        <v>0.1143707025093414</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8978842146046808</v>
+        <v>0.8836320842141304</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1504207367285236</v>
+        <v>0.1514307367285236</v>
       </c>
       <c r="C65">
-        <v>20.0351173692525</v>
+        <v>15.7116353624985</v>
       </c>
       <c r="D65">
-        <v>170.9421173692525</v>
+        <v>169.3076353624985</v>
       </c>
       <c r="E65">
-        <v>67.50699999999998</v>
+        <v>70.19599999999997</v>
       </c>
       <c r="F65">
-        <v>169.407</v>
+        <v>172.096</v>
       </c>
       <c r="G65">
         <v>18.5</v>
@@ -6611,37 +6611,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M65">
-        <v>24.8689476</v>
+        <v>25.2636928</v>
       </c>
       <c r="N65">
-        <v>-2.893947600000004</v>
+        <v>-3.288692800000003</v>
       </c>
       <c r="O65">
-        <v>-0.723486900000001</v>
+        <v>-0.8221732000000008</v>
       </c>
       <c r="P65">
-        <v>-2.170460700000003</v>
+        <v>-2.466519600000002</v>
       </c>
       <c r="Q65">
-        <v>15.7295393</v>
+        <v>15.4334804</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.21180322742605</v>
+        <v>0.2164144281878848</v>
       </c>
       <c r="T65">
-        <v>1.988675889605204</v>
+        <v>2.043916886538682</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2209080210535326</v>
+        <v>0.2174563332245712</v>
       </c>
       <c r="W65">
-        <v>0.1143707025093414</v>
+        <v>0.114877410282633</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8836320842141304</v>
+        <v>0.8698253328982846</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1514307367285236</v>
+        <v>0.1524407367285236</v>
       </c>
       <c r="C66">
-        <v>15.7116353624985</v>
+        <v>11.41911388504053</v>
       </c>
       <c r="D66">
-        <v>169.3076353624985</v>
+        <v>167.7041138850405</v>
       </c>
       <c r="E66">
-        <v>70.19599999999997</v>
+        <v>72.88499999999999</v>
       </c>
       <c r="F66">
-        <v>172.096</v>
+        <v>174.785</v>
       </c>
       <c r="G66">
         <v>18.5</v>
@@ -6693,37 +6693,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M66">
-        <v>25.2636928</v>
+        <v>25.658438</v>
       </c>
       <c r="N66">
-        <v>-3.288692800000003</v>
+        <v>-3.683438000000006</v>
       </c>
       <c r="O66">
-        <v>-0.8221732000000008</v>
+        <v>-0.9208595000000015</v>
       </c>
       <c r="P66">
-        <v>-2.466519600000002</v>
+        <v>-2.762578500000004</v>
       </c>
       <c r="Q66">
-        <v>15.4334804</v>
+        <v>15.13742149999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2164144281878848</v>
+        <v>0.2212891261361101</v>
       </c>
       <c r="T66">
-        <v>2.043916886538682</v>
+        <v>2.102314511868359</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2174563332245712</v>
+        <v>0.2141108511749623</v>
       </c>
       <c r="W66">
-        <v>0.114877410282633</v>
+        <v>0.1153685270475155</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8698253328982846</v>
+        <v>0.8564434046998494</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1524407367285236</v>
+        <v>0.1534507367285236</v>
       </c>
       <c r="C67">
-        <v>11.41911388504053</v>
+        <v>7.156681503885181</v>
       </c>
       <c r="D67">
-        <v>167.7041138850405</v>
+        <v>166.1306815038852</v>
       </c>
       <c r="E67">
-        <v>72.88499999999999</v>
+        <v>75.57399999999998</v>
       </c>
       <c r="F67">
-        <v>174.785</v>
+        <v>177.474</v>
       </c>
       <c r="G67">
         <v>18.5</v>
@@ -6775,37 +6775,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M67">
-        <v>25.658438</v>
+        <v>26.0531832</v>
       </c>
       <c r="N67">
-        <v>-3.683438000000006</v>
+        <v>-4.078183200000005</v>
       </c>
       <c r="O67">
-        <v>-0.9208595000000015</v>
+        <v>-1.019545800000001</v>
       </c>
       <c r="P67">
-        <v>-2.762578500000004</v>
+        <v>-3.058637400000004</v>
       </c>
       <c r="Q67">
-        <v>15.13742149999999</v>
+        <v>14.84136259999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2212891261361101</v>
+        <v>0.2264505710224662</v>
       </c>
       <c r="T67">
-        <v>2.102314511868359</v>
+        <v>2.164147291629193</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2141108511749623</v>
+        <v>0.2108667473692811</v>
       </c>
       <c r="W67">
-        <v>0.1153685270475155</v>
+        <v>0.1158447614861895</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8564434046998494</v>
+        <v>0.8434669894771244</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1534507367285236</v>
+        <v>0.1544607367285236</v>
       </c>
       <c r="C68">
-        <v>7.156681503885181</v>
+        <v>2.923499185867826</v>
       </c>
       <c r="D68">
-        <v>166.1306815038852</v>
+        <v>164.5864991858678</v>
       </c>
       <c r="E68">
-        <v>75.57399999999998</v>
+        <v>78.26299999999998</v>
       </c>
       <c r="F68">
-        <v>177.474</v>
+        <v>180.163</v>
       </c>
       <c r="G68">
         <v>18.5</v>
@@ -6857,37 +6857,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M68">
-        <v>26.0531832</v>
+        <v>26.4479284</v>
       </c>
       <c r="N68">
-        <v>-4.078183200000005</v>
+        <v>-4.472928400000004</v>
       </c>
       <c r="O68">
-        <v>-1.019545800000001</v>
+        <v>-1.118232100000001</v>
       </c>
       <c r="P68">
-        <v>-3.058637400000004</v>
+        <v>-3.354696300000003</v>
       </c>
       <c r="Q68">
-        <v>14.84136259999999</v>
+        <v>14.54530369999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2264505710224662</v>
+        <v>0.2319248307504198</v>
       </c>
       <c r="T68">
-        <v>2.164147291629193</v>
+        <v>2.229727512587653</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2108667473692811</v>
+        <v>0.2077194824831724</v>
       </c>
       <c r="W68">
-        <v>0.1158447614861895</v>
+        <v>0.1163067799714703</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8434669894771244</v>
+        <v>0.8308779299326897</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1544607367285236</v>
+        <v>0.1554707367285236</v>
       </c>
       <c r="C69">
-        <v>2.923499185867826</v>
+        <v>-1.281241194259422</v>
       </c>
       <c r="D69">
-        <v>164.5864991858678</v>
+        <v>163.0707588057406</v>
       </c>
       <c r="E69">
-        <v>78.26299999999998</v>
+        <v>80.952</v>
       </c>
       <c r="F69">
-        <v>180.163</v>
+        <v>182.852</v>
       </c>
       <c r="G69">
         <v>18.5</v>
@@ -6939,37 +6939,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M69">
-        <v>26.4479284</v>
+        <v>26.8426736</v>
       </c>
       <c r="N69">
-        <v>-4.472928400000004</v>
+        <v>-4.86767360000001</v>
       </c>
       <c r="O69">
-        <v>-1.118232100000001</v>
+        <v>-1.216918400000003</v>
       </c>
       <c r="P69">
-        <v>-3.354696300000003</v>
+        <v>-3.650755200000008</v>
       </c>
       <c r="Q69">
-        <v>14.54530369999999</v>
+        <v>14.24924479999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2319248307504198</v>
+        <v>0.2377412317113704</v>
       </c>
       <c r="T69">
-        <v>2.229727512587653</v>
+        <v>2.299406497356018</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2077194824831724</v>
+        <v>0.204664784211361</v>
       </c>
       <c r="W69">
-        <v>0.1163067799714703</v>
+        <v>0.1167552096777722</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8308779299326897</v>
+        <v>0.8186591368454441</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1554707367285236</v>
+        <v>0.1564807367285236</v>
       </c>
       <c r="C70">
-        <v>-1.281241194259422</v>
+        <v>-5.458318264055009</v>
       </c>
       <c r="D70">
-        <v>163.0707588057406</v>
+        <v>161.582681735945</v>
       </c>
       <c r="E70">
-        <v>80.952</v>
+        <v>83.64099999999999</v>
       </c>
       <c r="F70">
-        <v>182.852</v>
+        <v>185.541</v>
       </c>
       <c r="G70">
         <v>18.5</v>
@@ -7021,37 +7021,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M70">
-        <v>26.8426736</v>
+        <v>27.2374188</v>
       </c>
       <c r="N70">
-        <v>-4.86767360000001</v>
+        <v>-5.262418800000006</v>
       </c>
       <c r="O70">
-        <v>-1.216918400000003</v>
+        <v>-1.315604700000002</v>
       </c>
       <c r="P70">
-        <v>-3.650755200000008</v>
+        <v>-3.946814100000005</v>
       </c>
       <c r="Q70">
-        <v>14.24924479999999</v>
+        <v>13.95318589999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2377412317113704</v>
+        <v>0.2439328843472211</v>
       </c>
       <c r="T70">
-        <v>2.299406497356018</v>
+        <v>2.373580900496535</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.204664784211361</v>
+        <v>0.2016986279184428</v>
       </c>
       <c r="W70">
-        <v>0.1167552096777722</v>
+        <v>0.1171906414215726</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8186591368454441</v>
+        <v>0.8067945116737711</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1564807367285236</v>
+        <v>0.1979611838562825</v>
       </c>
       <c r="C71">
-        <v>-5.458318264055009</v>
+        <v>-52.19614672769225</v>
       </c>
       <c r="D71">
-        <v>161.582681735945</v>
+        <v>117.5338532723077</v>
       </c>
       <c r="E71">
-        <v>83.64099999999999</v>
+        <v>86.32999999999998</v>
       </c>
       <c r="F71">
-        <v>185.541</v>
+        <v>188.23</v>
       </c>
       <c r="G71">
         <v>18.5</v>
@@ -7103,45 +7103,45 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M71">
-        <v>27.2374188</v>
+        <v>37.796584</v>
       </c>
       <c r="N71">
-        <v>-5.262418800000006</v>
+        <v>-15.821584</v>
       </c>
       <c r="O71">
-        <v>-1.315604700000002</v>
+        <v>-3.955396</v>
       </c>
       <c r="P71">
-        <v>-3.946814100000005</v>
+        <v>-11.866188</v>
       </c>
       <c r="Q71">
-        <v>13.95318589999999</v>
+        <v>6.033811999999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2439328843472211</v>
+        <v>0.2594388042513248</v>
       </c>
       <c r="T71">
-        <v>2.373580900496535</v>
+        <v>2.55933782545257</v>
       </c>
       <c r="U71">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.2016986279184428</v>
+        <v>0.1453504369601231</v>
       </c>
       <c r="W71">
-        <v>0.1171906414215726</v>
+        <v>0.1716136322584073</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.8067945116737711</v>
+        <v>0.5814017478404926</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1979611838562825</v>
+        <v>0.1995111838562826</v>
       </c>
       <c r="C72">
-        <v>-52.19614672769225</v>
+        <v>-56.07034007538269</v>
       </c>
       <c r="D72">
-        <v>117.5338532723077</v>
+        <v>116.3486599246173</v>
       </c>
       <c r="E72">
-        <v>86.32999999999998</v>
+        <v>89.01900000000001</v>
       </c>
       <c r="F72">
-        <v>188.23</v>
+        <v>190.919</v>
       </c>
       <c r="G72">
         <v>18.5</v>
@@ -7185,37 +7185,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M72">
-        <v>37.796584</v>
+        <v>38.3365352</v>
       </c>
       <c r="N72">
-        <v>-15.821584</v>
+        <v>-16.36153520000001</v>
       </c>
       <c r="O72">
-        <v>-3.955396</v>
+        <v>-4.090383800000001</v>
       </c>
       <c r="P72">
-        <v>-11.866188</v>
+        <v>-12.2711514</v>
       </c>
       <c r="Q72">
-        <v>6.033811999999998</v>
+        <v>5.628848599999994</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2594388042513248</v>
+        <v>0.2668056595703361</v>
       </c>
       <c r="T72">
-        <v>2.55933782545257</v>
+        <v>2.647590853916453</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1453504369601231</v>
+        <v>0.1433032477071637</v>
       </c>
       <c r="W72">
-        <v>0.1716136322584073</v>
+        <v>0.1720247078604016</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5814017478404926</v>
+        <v>0.5732129908286546</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1995111838562825</v>
+        <v>0.2010611838562825</v>
       </c>
       <c r="C73">
-        <v>-56.07034007538263</v>
+        <v>-59.92086943129746</v>
       </c>
       <c r="D73">
-        <v>116.3486599246174</v>
+        <v>115.1871305687025</v>
       </c>
       <c r="E73">
-        <v>89.01899999999998</v>
+        <v>91.70799999999997</v>
       </c>
       <c r="F73">
-        <v>190.919</v>
+        <v>193.608</v>
       </c>
       <c r="G73">
         <v>18.5</v>
@@ -7267,37 +7267,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M73">
-        <v>38.3365352</v>
+        <v>38.8764864</v>
       </c>
       <c r="N73">
-        <v>-16.36153520000001</v>
+        <v>-16.9014864</v>
       </c>
       <c r="O73">
-        <v>-4.090383800000001</v>
+        <v>-4.225371600000001</v>
       </c>
       <c r="P73">
-        <v>-12.2711514</v>
+        <v>-12.6761148</v>
       </c>
       <c r="Q73">
-        <v>5.628848599999994</v>
+        <v>5.223885199999996</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.266805659570336</v>
+        <v>0.2746987188407052</v>
       </c>
       <c r="T73">
-        <v>2.647590853916452</v>
+        <v>2.742147670127754</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1433032477071637</v>
+        <v>0.141312924822342</v>
       </c>
       <c r="W73">
-        <v>0.1720247078604016</v>
+        <v>0.1724243646956737</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5732129908286546</v>
+        <v>0.5652516992893677</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2010611838562825</v>
+        <v>0.2026111838562825</v>
       </c>
       <c r="C74">
-        <v>-59.92086943129746</v>
+        <v>-63.74843651555028</v>
       </c>
       <c r="D74">
-        <v>115.1871305687025</v>
+        <v>114.0485634844497</v>
       </c>
       <c r="E74">
-        <v>91.70799999999997</v>
+        <v>94.39699999999996</v>
       </c>
       <c r="F74">
-        <v>193.608</v>
+        <v>196.297</v>
       </c>
       <c r="G74">
         <v>18.5</v>
@@ -7349,37 +7349,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M74">
-        <v>38.8764864</v>
+        <v>39.41643759999999</v>
       </c>
       <c r="N74">
-        <v>-16.9014864</v>
+        <v>-17.4414376</v>
       </c>
       <c r="O74">
-        <v>-4.225371600000001</v>
+        <v>-4.3603594</v>
       </c>
       <c r="P74">
-        <v>-12.6761148</v>
+        <v>-13.0810782</v>
       </c>
       <c r="Q74">
-        <v>5.223885199999996</v>
+        <v>4.818921799999998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2746987188407052</v>
+        <v>0.2831764491681387</v>
       </c>
       <c r="T74">
-        <v>2.742147670127754</v>
+        <v>2.8437086949473</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.141312924822342</v>
+        <v>0.1393771313316249</v>
       </c>
       <c r="W74">
-        <v>0.1724243646956737</v>
+        <v>0.1728130720286097</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5652516992893677</v>
+        <v>0.5575085253264997</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2026111838562825</v>
+        <v>0.2041611838562826</v>
       </c>
       <c r="C75">
-        <v>-63.74843651555028</v>
+        <v>-67.55371557520505</v>
       </c>
       <c r="D75">
-        <v>114.0485634844497</v>
+        <v>112.932284424795</v>
       </c>
       <c r="E75">
-        <v>94.39699999999996</v>
+        <v>97.08599999999998</v>
       </c>
       <c r="F75">
-        <v>196.297</v>
+        <v>198.986</v>
       </c>
       <c r="G75">
         <v>18.5</v>
@@ -7431,37 +7431,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M75">
-        <v>39.41643759999999</v>
+        <v>39.9563888</v>
       </c>
       <c r="N75">
-        <v>-17.4414376</v>
+        <v>-17.9813888</v>
       </c>
       <c r="O75">
-        <v>-4.3603594</v>
+        <v>-4.495347200000001</v>
       </c>
       <c r="P75">
-        <v>-13.0810782</v>
+        <v>-13.4860416</v>
       </c>
       <c r="Q75">
-        <v>4.818921799999998</v>
+        <v>4.413958399999995</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2831764491681387</v>
+        <v>0.2923063125976825</v>
       </c>
       <c r="T75">
-        <v>2.8437086949473</v>
+        <v>2.953082106291427</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1393771313316249</v>
+        <v>0.1374936565839003</v>
       </c>
       <c r="W75">
-        <v>0.1728130720286097</v>
+        <v>0.1731912737579528</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5575085253264997</v>
+        <v>0.5499746263356011</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2041611838562826</v>
+        <v>0.2057111838562825</v>
       </c>
       <c r="C76">
-        <v>-67.55371557520505</v>
+        <v>-71.33735471574036</v>
       </c>
       <c r="D76">
-        <v>112.932284424795</v>
+        <v>111.8376452842596</v>
       </c>
       <c r="E76">
-        <v>97.08599999999998</v>
+        <v>99.77499999999998</v>
       </c>
       <c r="F76">
-        <v>198.986</v>
+        <v>201.675</v>
       </c>
       <c r="G76">
         <v>18.5</v>
@@ -7513,37 +7513,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M76">
-        <v>39.9563888</v>
+        <v>40.49634</v>
       </c>
       <c r="N76">
-        <v>-17.9813888</v>
+        <v>-18.52134</v>
       </c>
       <c r="O76">
-        <v>-4.495347200000001</v>
+        <v>-4.630335000000001</v>
       </c>
       <c r="P76">
-        <v>-13.4860416</v>
+        <v>-13.891005</v>
       </c>
       <c r="Q76">
-        <v>4.413958399999995</v>
+        <v>4.008994999999997</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2923063125976825</v>
+        <v>0.3021665651015897</v>
       </c>
       <c r="T76">
-        <v>2.953082106291427</v>
+        <v>3.071205390543084</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1374936565839003</v>
+        <v>0.1356604078294483</v>
       </c>
       <c r="W76">
-        <v>0.1731912737579528</v>
+        <v>0.1735593901078468</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5499746263356011</v>
+        <v>0.5426416313177931</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2057111838562825</v>
+        <v>0.2072611838562826</v>
       </c>
       <c r="C77">
-        <v>-71.33735471574036</v>
+        <v>-75.09997715582421</v>
       </c>
       <c r="D77">
-        <v>111.8376452842596</v>
+        <v>110.7640228441758</v>
       </c>
       <c r="E77">
-        <v>99.77499999999998</v>
+        <v>102.464</v>
       </c>
       <c r="F77">
-        <v>201.675</v>
+        <v>204.364</v>
       </c>
       <c r="G77">
         <v>18.5</v>
@@ -7595,37 +7595,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M77">
-        <v>40.49634</v>
+        <v>41.03629119999999</v>
       </c>
       <c r="N77">
-        <v>-18.52134</v>
+        <v>-19.0612912</v>
       </c>
       <c r="O77">
-        <v>-4.630335000000001</v>
+        <v>-4.7653228</v>
       </c>
       <c r="P77">
-        <v>-13.891005</v>
+        <v>-14.2959684</v>
       </c>
       <c r="Q77">
-        <v>4.008994999999997</v>
+        <v>3.604031599999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3021665651015897</v>
+        <v>0.312848505314156</v>
       </c>
       <c r="T77">
-        <v>3.071205390543084</v>
+        <v>3.199172281815713</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1356604078294483</v>
+        <v>0.1338754024632713</v>
       </c>
       <c r="W77">
-        <v>0.1735593901078468</v>
+        <v>0.1739178191853751</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5426416313177931</v>
+        <v>0.5355016098530854</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2072611838562826</v>
+        <v>0.2088111838562825</v>
       </c>
       <c r="C78">
-        <v>-75.09997715582421</v>
+        <v>-78.84218241050067</v>
       </c>
       <c r="D78">
-        <v>110.7640228441758</v>
+        <v>109.7108175894993</v>
       </c>
       <c r="E78">
-        <v>102.464</v>
+        <v>105.153</v>
       </c>
       <c r="F78">
-        <v>204.364</v>
+        <v>207.053</v>
       </c>
       <c r="G78">
         <v>18.5</v>
@@ -7677,37 +7677,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M78">
-        <v>41.03629119999999</v>
+        <v>41.5762424</v>
       </c>
       <c r="N78">
-        <v>-19.0612912</v>
+        <v>-19.6012424</v>
       </c>
       <c r="O78">
-        <v>-4.7653228</v>
+        <v>-4.900310600000001</v>
       </c>
       <c r="P78">
-        <v>-14.2959684</v>
+        <v>-14.7009318</v>
       </c>
       <c r="Q78">
-        <v>3.604031599999999</v>
+        <v>3.199068199999996</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.312848505314156</v>
+        <v>0.3244593098930324</v>
       </c>
       <c r="T78">
-        <v>3.199172281815713</v>
+        <v>3.338266728851179</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1338754024632713</v>
+        <v>0.1321367608728392</v>
       </c>
       <c r="W78">
-        <v>0.1739178191853751</v>
+        <v>0.1742669384167339</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5355016098530854</v>
+        <v>0.5285470434913568</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2088111838562825</v>
+        <v>0.2103611838562826</v>
       </c>
       <c r="C79">
-        <v>-78.84218241050067</v>
+        <v>-82.56454740751137</v>
       </c>
       <c r="D79">
-        <v>109.7108175894993</v>
+        <v>108.6774525924886</v>
       </c>
       <c r="E79">
-        <v>105.153</v>
+        <v>107.842</v>
       </c>
       <c r="F79">
-        <v>207.053</v>
+        <v>209.742</v>
       </c>
       <c r="G79">
         <v>18.5</v>
@@ -7759,37 +7759,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M79">
-        <v>41.5762424</v>
+        <v>42.1161936</v>
       </c>
       <c r="N79">
-        <v>-19.6012424</v>
+        <v>-20.14119360000001</v>
       </c>
       <c r="O79">
-        <v>-4.900310600000001</v>
+        <v>-5.035298400000002</v>
       </c>
       <c r="P79">
-        <v>-14.7009318</v>
+        <v>-15.10589520000001</v>
       </c>
       <c r="Q79">
-        <v>3.199068199999996</v>
+        <v>2.794104799999992</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3244593098930324</v>
+        <v>0.3371256421608975</v>
       </c>
       <c r="T79">
-        <v>3.338266728851179</v>
+        <v>3.490006125617142</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1321367608728392</v>
+        <v>0.1304426998360079</v>
       </c>
       <c r="W79">
-        <v>0.1742669384167339</v>
+        <v>0.1746071058729296</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5285470434913568</v>
+        <v>0.5217707993440317</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2103611838562826</v>
+        <v>0.2119111838562825</v>
       </c>
       <c r="C80">
-        <v>-82.56454740751137</v>
+        <v>-86.26762754111692</v>
       </c>
       <c r="D80">
-        <v>108.6774525924886</v>
+        <v>107.6633724588831</v>
       </c>
       <c r="E80">
-        <v>107.842</v>
+        <v>110.531</v>
       </c>
       <c r="F80">
-        <v>209.742</v>
+        <v>212.431</v>
       </c>
       <c r="G80">
         <v>18.5</v>
@@ -7841,37 +7841,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M80">
-        <v>42.1161936</v>
+        <v>42.6561448</v>
       </c>
       <c r="N80">
-        <v>-20.14119360000001</v>
+        <v>-20.68114480000001</v>
       </c>
       <c r="O80">
-        <v>-5.035298400000002</v>
+        <v>-5.170286200000001</v>
       </c>
       <c r="P80">
-        <v>-15.10589520000001</v>
+        <v>-15.5108586</v>
       </c>
       <c r="Q80">
-        <v>2.794104799999992</v>
+        <v>2.389141399999994</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3371256421608975</v>
+        <v>0.3509982917876069</v>
       </c>
       <c r="T80">
-        <v>3.490006125617142</v>
+        <v>3.656196893503673</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1304426998360079</v>
+        <v>0.1287915264203623</v>
       </c>
       <c r="W80">
-        <v>0.1746071058729296</v>
+        <v>0.1749386614947913</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5217707993440317</v>
+        <v>0.515166105681449</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2119111838562825</v>
+        <v>0.2134611838562825</v>
       </c>
       <c r="C81">
-        <v>-86.26762754111692</v>
+        <v>-89.9519576674646</v>
       </c>
       <c r="D81">
-        <v>107.6633724588831</v>
+        <v>106.6680423325354</v>
       </c>
       <c r="E81">
-        <v>110.531</v>
+        <v>113.22</v>
       </c>
       <c r="F81">
-        <v>212.431</v>
+        <v>215.12</v>
       </c>
       <c r="G81">
         <v>18.5</v>
@@ -7923,37 +7923,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M81">
-        <v>42.6561448</v>
+        <v>43.196096</v>
       </c>
       <c r="N81">
-        <v>-20.68114480000001</v>
+        <v>-21.22109600000001</v>
       </c>
       <c r="O81">
-        <v>-5.170286200000001</v>
+        <v>-5.305274000000002</v>
       </c>
       <c r="P81">
-        <v>-15.5108586</v>
+        <v>-15.91582200000001</v>
       </c>
       <c r="Q81">
-        <v>2.389141399999994</v>
+        <v>1.984177999999991</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3509982917876069</v>
+        <v>0.3662582063769872</v>
       </c>
       <c r="T81">
-        <v>3.656196893503673</v>
+        <v>3.839006738178856</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1287915264203623</v>
+        <v>0.1271816323401077</v>
       </c>
       <c r="W81">
-        <v>0.1749386614947913</v>
+        <v>0.1752619282261064</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.515166105681449</v>
+        <v>0.5087265293604308</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2134611838562825</v>
+        <v>0.2150111838562826</v>
       </c>
       <c r="C82">
-        <v>-89.9519576674646</v>
+        <v>-93.61805304524917</v>
       </c>
       <c r="D82">
-        <v>106.6680423325354</v>
+        <v>105.6909469547508</v>
       </c>
       <c r="E82">
-        <v>113.22</v>
+        <v>115.909</v>
       </c>
       <c r="F82">
-        <v>215.12</v>
+        <v>217.809</v>
       </c>
       <c r="G82">
         <v>18.5</v>
@@ -8005,37 +8005,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M82">
-        <v>43.196096</v>
+        <v>43.7360472</v>
       </c>
       <c r="N82">
-        <v>-21.22109600000001</v>
+        <v>-21.76104720000001</v>
       </c>
       <c r="O82">
-        <v>-5.305274000000002</v>
+        <v>-5.440261800000002</v>
       </c>
       <c r="P82">
-        <v>-15.91582200000001</v>
+        <v>-16.32078540000001</v>
       </c>
       <c r="Q82">
-        <v>1.984177999999991</v>
+        <v>1.579214599999993</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3662582063769872</v>
+        <v>0.3831244277652498</v>
       </c>
       <c r="T82">
-        <v>3.839006738178856</v>
+        <v>4.041059724398797</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1271816323401077</v>
+        <v>0.1256114887309706</v>
       </c>
       <c r="W82">
-        <v>0.1752619282261064</v>
+        <v>0.1755772130628211</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5087265293604308</v>
+        <v>0.5024459549238824</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2150111838562826</v>
+        <v>0.2463387415277575</v>
       </c>
       <c r="C83">
-        <v>-93.61805304524917</v>
+        <v>-112.8177741700223</v>
       </c>
       <c r="D83">
-        <v>105.6909469547508</v>
+        <v>89.18022582997773</v>
       </c>
       <c r="E83">
-        <v>115.909</v>
+        <v>118.598</v>
       </c>
       <c r="F83">
-        <v>217.809</v>
+        <v>220.498</v>
       </c>
       <c r="G83">
         <v>18.5</v>
@@ -8087,45 +8087,45 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M83">
-        <v>43.7360472</v>
+        <v>51.9934284</v>
       </c>
       <c r="N83">
-        <v>-21.76104720000001</v>
+        <v>-30.0184284</v>
       </c>
       <c r="O83">
-        <v>-5.440261800000002</v>
+        <v>-7.504607100000001</v>
       </c>
       <c r="P83">
-        <v>-16.32078540000001</v>
+        <v>-22.5138213</v>
       </c>
       <c r="Q83">
-        <v>1.579214599999993</v>
+        <v>-4.613821300000005</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3831244277652498</v>
+        <v>0.4078511052604025</v>
       </c>
       <c r="T83">
-        <v>4.041059724398797</v>
+        <v>4.337278949332596</v>
       </c>
       <c r="U83">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1256114887309706</v>
+        <v>0.1056623917494927</v>
       </c>
       <c r="W83">
-        <v>0.1755772130628211</v>
+        <v>0.2108848080254696</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.5024459549238824</v>
+        <v>0.4226495669979707</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2463387415277575</v>
+        <v>0.2482387415277575</v>
       </c>
       <c r="C84">
-        <v>-112.8177741700223</v>
+        <v>-116.3437801096869</v>
       </c>
       <c r="D84">
-        <v>89.18022582997773</v>
+        <v>88.34321989031312</v>
       </c>
       <c r="E84">
-        <v>118.598</v>
+        <v>121.287</v>
       </c>
       <c r="F84">
-        <v>220.498</v>
+        <v>223.187</v>
       </c>
       <c r="G84">
         <v>18.5</v>
@@ -8169,37 +8169,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M84">
-        <v>51.9934284</v>
+        <v>52.62749460000001</v>
       </c>
       <c r="N84">
-        <v>-30.0184284</v>
+        <v>-30.65249460000001</v>
       </c>
       <c r="O84">
-        <v>-7.504607100000001</v>
+        <v>-7.663123650000003</v>
       </c>
       <c r="P84">
-        <v>-22.5138213</v>
+        <v>-22.98937095000001</v>
       </c>
       <c r="Q84">
-        <v>-4.613821300000005</v>
+        <v>-5.08937095000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4078511052604025</v>
+        <v>0.4291482290992498</v>
       </c>
       <c r="T84">
-        <v>4.337278949332596</v>
+        <v>4.592413005175691</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1056623917494927</v>
+        <v>0.1043893508850409</v>
       </c>
       <c r="W84">
-        <v>0.2108848080254696</v>
+        <v>0.2111849910613073</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4226495669979707</v>
+        <v>0.4175574035401638</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2482387415277575</v>
+        <v>0.2501387415277576</v>
       </c>
       <c r="C85">
-        <v>-116.3437801096869</v>
+        <v>-119.8542206086184</v>
       </c>
       <c r="D85">
-        <v>88.34321989031312</v>
+        <v>87.52177939138163</v>
       </c>
       <c r="E85">
-        <v>121.287</v>
+        <v>123.976</v>
       </c>
       <c r="F85">
-        <v>223.187</v>
+        <v>225.876</v>
       </c>
       <c r="G85">
         <v>18.5</v>
@@ -8251,37 +8251,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M85">
-        <v>52.62749460000001</v>
+        <v>53.26156080000001</v>
       </c>
       <c r="N85">
-        <v>-30.65249460000001</v>
+        <v>-31.28656080000001</v>
       </c>
       <c r="O85">
-        <v>-7.663123650000003</v>
+        <v>-7.821640200000003</v>
       </c>
       <c r="P85">
-        <v>-22.98937095000001</v>
+        <v>-23.46492060000001</v>
       </c>
       <c r="Q85">
-        <v>-5.08937095000001</v>
+        <v>-5.564920600000008</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4291482290992498</v>
+        <v>0.453107493417953</v>
       </c>
       <c r="T85">
-        <v>4.592413005175691</v>
+        <v>4.879438817999173</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1043893508850409</v>
+        <v>0.1031466205173619</v>
       </c>
       <c r="W85">
-        <v>0.2111849910613073</v>
+        <v>0.2114780268820061</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4175574035401638</v>
+        <v>0.4125864820694476</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2501387415277575</v>
+        <v>0.2520387415277576</v>
       </c>
       <c r="C86">
-        <v>-119.8542206086183</v>
+        <v>-123.3495258624799</v>
       </c>
       <c r="D86">
-        <v>87.52177939138166</v>
+        <v>86.71547413752009</v>
       </c>
       <c r="E86">
-        <v>123.976</v>
+        <v>126.665</v>
       </c>
       <c r="F86">
-        <v>225.876</v>
+        <v>228.565</v>
       </c>
       <c r="G86">
         <v>18.5</v>
@@ -8333,37 +8333,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M86">
-        <v>53.2615608</v>
+        <v>53.895627</v>
       </c>
       <c r="N86">
-        <v>-31.2865608</v>
+        <v>-31.920627</v>
       </c>
       <c r="O86">
-        <v>-7.821640200000001</v>
+        <v>-7.980156750000001</v>
       </c>
       <c r="P86">
-        <v>-23.4649206</v>
+        <v>-23.94047025</v>
       </c>
       <c r="Q86">
-        <v>-5.564920600000004</v>
+        <v>-6.040470250000006</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4531074934179527</v>
+        <v>0.4802613263124829</v>
       </c>
       <c r="T86">
-        <v>4.879438817999169</v>
+        <v>5.204734739199114</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1031466205173619</v>
+        <v>0.1019331308642165</v>
       </c>
       <c r="W86">
-        <v>0.2114780268820061</v>
+        <v>0.2117641677422178</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4125864820694476</v>
+        <v>0.4077325234568659</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2520387415277576</v>
+        <v>0.2539387415277575</v>
       </c>
       <c r="C87">
-        <v>-123.3495258624799</v>
+        <v>-126.8301103587248</v>
       </c>
       <c r="D87">
-        <v>86.71547413752009</v>
+        <v>85.92388964127524</v>
       </c>
       <c r="E87">
-        <v>126.665</v>
+        <v>129.354</v>
       </c>
       <c r="F87">
-        <v>228.565</v>
+        <v>231.254</v>
       </c>
       <c r="G87">
         <v>18.5</v>
@@ -8415,37 +8415,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M87">
-        <v>53.895627</v>
+        <v>54.5296932</v>
       </c>
       <c r="N87">
-        <v>-31.920627</v>
+        <v>-32.5546932</v>
       </c>
       <c r="O87">
-        <v>-7.980156750000001</v>
+        <v>-8.138673300000001</v>
       </c>
       <c r="P87">
-        <v>-23.94047025</v>
+        <v>-24.4160199</v>
       </c>
       <c r="Q87">
-        <v>-6.040470250000006</v>
+        <v>-6.516019900000003</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4802613263124829</v>
+        <v>0.511294278191946</v>
       </c>
       <c r="T87">
-        <v>5.204734739199114</v>
+        <v>5.576501506284765</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1019331308642165</v>
+        <v>0.1007478619006791</v>
       </c>
       <c r="W87">
-        <v>0.2117641677422178</v>
+        <v>0.2120436541638199</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4077325234568659</v>
+        <v>0.4029914476027163</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2539387415277575</v>
+        <v>0.2558387415277575</v>
       </c>
       <c r="C88">
-        <v>-126.8301103587248</v>
+        <v>-130.2963735870747</v>
       </c>
       <c r="D88">
-        <v>85.92388964127524</v>
+        <v>85.1466264129253</v>
       </c>
       <c r="E88">
-        <v>129.354</v>
+        <v>132.043</v>
       </c>
       <c r="F88">
-        <v>231.254</v>
+        <v>233.943</v>
       </c>
       <c r="G88">
         <v>18.5</v>
@@ -8497,37 +8497,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M88">
-        <v>54.5296932</v>
+        <v>55.1637594</v>
       </c>
       <c r="N88">
-        <v>-32.5546932</v>
+        <v>-33.1887594</v>
       </c>
       <c r="O88">
-        <v>-8.138673300000001</v>
+        <v>-8.297189850000001</v>
       </c>
       <c r="P88">
-        <v>-24.4160199</v>
+        <v>-24.89156955</v>
       </c>
       <c r="Q88">
-        <v>-6.516019900000003</v>
+        <v>-6.991569550000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.511294278191946</v>
+        <v>0.5471015303605572</v>
       </c>
       <c r="T88">
-        <v>5.576501506284765</v>
+        <v>6.005463160614362</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1007478619006791</v>
+        <v>0.09958984049952184</v>
       </c>
       <c r="W88">
-        <v>0.2120436541638199</v>
+        <v>0.2123167156102128</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4029914476027163</v>
+        <v>0.3983593619980874</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2558387415277575</v>
+        <v>0.2577387415277576</v>
       </c>
       <c r="C89">
-        <v>-130.2963735870747</v>
+        <v>-133.7487007117824</v>
       </c>
       <c r="D89">
-        <v>85.1466264129253</v>
+        <v>84.38329928821756</v>
       </c>
       <c r="E89">
-        <v>132.043</v>
+        <v>134.732</v>
       </c>
       <c r="F89">
-        <v>233.943</v>
+        <v>236.632</v>
       </c>
       <c r="G89">
         <v>18.5</v>
@@ -8579,37 +8579,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M89">
-        <v>55.1637594</v>
+        <v>55.7978256</v>
       </c>
       <c r="N89">
-        <v>-33.1887594</v>
+        <v>-33.8228256</v>
       </c>
       <c r="O89">
-        <v>-8.297189850000001</v>
+        <v>-8.4557064</v>
       </c>
       <c r="P89">
-        <v>-24.89156955</v>
+        <v>-25.3671192</v>
       </c>
       <c r="Q89">
-        <v>-6.991569550000001</v>
+        <v>-7.467119200000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5471015303605572</v>
+        <v>0.5888766578906036</v>
       </c>
       <c r="T89">
-        <v>6.005463160614362</v>
+        <v>6.505918423998893</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09958984049952184</v>
+        <v>0.09845813776657274</v>
       </c>
       <c r="W89">
-        <v>0.2123167156102128</v>
+        <v>0.2125835711146422</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3983593619980874</v>
+        <v>0.3938325510662909</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2577387415277576</v>
+        <v>0.2596387415277576</v>
       </c>
       <c r="C90">
-        <v>-133.7487007117824</v>
+        <v>-137.1874632080549</v>
       </c>
       <c r="D90">
-        <v>84.38329928821756</v>
+        <v>83.63353679194509</v>
       </c>
       <c r="E90">
-        <v>134.732</v>
+        <v>137.421</v>
       </c>
       <c r="F90">
-        <v>236.632</v>
+        <v>239.321</v>
       </c>
       <c r="G90">
         <v>18.5</v>
@@ -8661,37 +8661,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M90">
-        <v>55.7978256</v>
+        <v>56.4318918</v>
       </c>
       <c r="N90">
-        <v>-33.8228256</v>
+        <v>-34.4568918</v>
       </c>
       <c r="O90">
-        <v>-8.4557064</v>
+        <v>-8.61422295</v>
       </c>
       <c r="P90">
-        <v>-25.3671192</v>
+        <v>-25.84266885</v>
       </c>
       <c r="Q90">
-        <v>-7.467119200000003</v>
+        <v>-7.942668850000004</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5888766578906036</v>
+        <v>0.6382472631533859</v>
       </c>
       <c r="T90">
-        <v>6.505918423998893</v>
+        <v>7.097365553453338</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09845813776657274</v>
+        <v>0.09735186655571237</v>
       </c>
       <c r="W90">
-        <v>0.2125835711146422</v>
+        <v>0.212844429866163</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3938325510662909</v>
+        <v>0.3894074662228495</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2596387415277576</v>
+        <v>0.2615387415277575</v>
       </c>
       <c r="C91">
-        <v>-137.1874632080549</v>
+        <v>-140.6130194648468</v>
       </c>
       <c r="D91">
-        <v>83.63353679194509</v>
+        <v>82.89698053515313</v>
       </c>
       <c r="E91">
-        <v>137.421</v>
+        <v>140.11</v>
       </c>
       <c r="F91">
-        <v>239.321</v>
+        <v>242.01</v>
       </c>
       <c r="G91">
         <v>18.5</v>
@@ -8743,37 +8743,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M91">
-        <v>56.4318918</v>
+        <v>57.065958</v>
       </c>
       <c r="N91">
-        <v>-34.4568918</v>
+        <v>-35.09095800000001</v>
       </c>
       <c r="O91">
-        <v>-8.61422295</v>
+        <v>-8.772739500000002</v>
       </c>
       <c r="P91">
-        <v>-25.84266885</v>
+        <v>-26.31821850000001</v>
       </c>
       <c r="Q91">
-        <v>-7.942668850000004</v>
+        <v>-8.418218500000009</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6382472631533859</v>
+        <v>0.6974919894687245</v>
       </c>
       <c r="T91">
-        <v>7.097365553453338</v>
+        <v>7.807102108798673</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09735186655571237</v>
+        <v>0.09627017914953777</v>
       </c>
       <c r="W91">
-        <v>0.212844429866163</v>
+        <v>0.213099491756539</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3894074662228495</v>
+        <v>0.3850807165981511</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2615387415277575</v>
+        <v>0.2634387415277575</v>
       </c>
       <c r="C92">
-        <v>-140.6130194648468</v>
+        <v>-144.02571535608</v>
       </c>
       <c r="D92">
-        <v>82.89698053515313</v>
+        <v>82.17328464391997</v>
       </c>
       <c r="E92">
-        <v>140.11</v>
+        <v>142.799</v>
       </c>
       <c r="F92">
-        <v>242.01</v>
+        <v>244.699</v>
       </c>
       <c r="G92">
         <v>18.5</v>
@@ -8825,37 +8825,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M92">
-        <v>57.065958</v>
+        <v>57.7000242</v>
       </c>
       <c r="N92">
-        <v>-35.09095800000001</v>
+        <v>-35.72502420000001</v>
       </c>
       <c r="O92">
-        <v>-8.772739500000002</v>
+        <v>-8.931256050000002</v>
       </c>
       <c r="P92">
-        <v>-26.31821850000001</v>
+        <v>-26.79376815000001</v>
       </c>
       <c r="Q92">
-        <v>-8.418218500000009</v>
+        <v>-8.893768150000007</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6974919894687245</v>
+        <v>0.769902210520805</v>
       </c>
       <c r="T92">
-        <v>7.807102108798673</v>
+        <v>8.674557898665192</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09627017914953777</v>
+        <v>0.09521226509294944</v>
       </c>
       <c r="W92">
-        <v>0.213099491756539</v>
+        <v>0.2133489478910825</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3850807165981511</v>
+        <v>0.3808490603717978</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2634387415277575</v>
+        <v>0.2653387415277575</v>
       </c>
       <c r="C93">
-        <v>-144.02571535608</v>
+        <v>-147.4258847822002</v>
       </c>
       <c r="D93">
-        <v>82.17328464391997</v>
+        <v>81.46211521779976</v>
       </c>
       <c r="E93">
-        <v>142.799</v>
+        <v>145.488</v>
       </c>
       <c r="F93">
-        <v>244.699</v>
+        <v>247.388</v>
       </c>
       <c r="G93">
         <v>18.5</v>
@@ -8907,37 +8907,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M93">
-        <v>57.7000242</v>
+        <v>58.33409039999999</v>
       </c>
       <c r="N93">
-        <v>-35.72502420000001</v>
+        <v>-36.3590904</v>
       </c>
       <c r="O93">
-        <v>-8.931256050000002</v>
+        <v>-9.0897726</v>
       </c>
       <c r="P93">
-        <v>-26.79376815000001</v>
+        <v>-27.2693178</v>
       </c>
       <c r="Q93">
-        <v>-8.893768150000007</v>
+        <v>-9.369317800000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.769902210520805</v>
+        <v>0.860414986835906</v>
       </c>
       <c r="T93">
-        <v>8.674557898665192</v>
+        <v>9.758877635998346</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09521226509294944</v>
+        <v>0.0941773491680261</v>
       </c>
       <c r="W93">
-        <v>0.2133489478910825</v>
+        <v>0.2135929810661794</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3808490603717978</v>
+        <v>0.3767093966721043</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2653387415277575</v>
+        <v>0.2672387415277575</v>
       </c>
       <c r="C94">
-        <v>-147.4258847822002</v>
+        <v>-150.8138501838547</v>
       </c>
       <c r="D94">
-        <v>81.46211521779976</v>
+        <v>80.76314981614529</v>
       </c>
       <c r="E94">
-        <v>145.488</v>
+        <v>148.177</v>
       </c>
       <c r="F94">
-        <v>247.388</v>
+        <v>250.077</v>
       </c>
       <c r="G94">
         <v>18.5</v>
@@ -8989,37 +8989,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M94">
-        <v>58.33409039999999</v>
+        <v>58.9681566</v>
       </c>
       <c r="N94">
-        <v>-36.3590904</v>
+        <v>-36.99315660000001</v>
       </c>
       <c r="O94">
-        <v>-9.0897726</v>
+        <v>-9.248289150000002</v>
       </c>
       <c r="P94">
-        <v>-27.2693178</v>
+        <v>-27.74486745</v>
       </c>
       <c r="Q94">
-        <v>-9.369317800000001</v>
+        <v>-9.844867450000006</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.860414986835906</v>
+        <v>0.9767885563838926</v>
       </c>
       <c r="T94">
-        <v>9.758877635998346</v>
+        <v>11.15300301256954</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0941773491680261</v>
+        <v>0.09316468949955269</v>
       </c>
       <c r="W94">
-        <v>0.2135929810661794</v>
+        <v>0.2138317662160055</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3767093966721043</v>
+        <v>0.3726587579982108</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2672387415277575</v>
+        <v>0.2691387415277575</v>
       </c>
       <c r="C95">
-        <v>-150.8138501838547</v>
+        <v>-154.1899230293494</v>
       </c>
       <c r="D95">
-        <v>80.76314981614529</v>
+        <v>80.07607697065059</v>
       </c>
       <c r="E95">
-        <v>148.177</v>
+        <v>150.866</v>
       </c>
       <c r="F95">
-        <v>250.077</v>
+        <v>252.766</v>
       </c>
       <c r="G95">
         <v>18.5</v>
@@ -9071,37 +9071,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M95">
-        <v>58.9681566</v>
+        <v>59.6022228</v>
       </c>
       <c r="N95">
-        <v>-36.99315660000001</v>
+        <v>-37.62722280000001</v>
       </c>
       <c r="O95">
-        <v>-9.248289150000002</v>
+        <v>-9.406805700000001</v>
       </c>
       <c r="P95">
-        <v>-27.74486745</v>
+        <v>-28.22041710000001</v>
       </c>
       <c r="Q95">
-        <v>-9.844867450000006</v>
+        <v>-10.32041710000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9767885563838926</v>
+        <v>1.131953315781208</v>
       </c>
       <c r="T95">
-        <v>11.15300301256954</v>
+        <v>13.0118368479978</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09316468949955269</v>
+        <v>0.09217357578147234</v>
       </c>
       <c r="W95">
-        <v>0.2138317662160055</v>
+        <v>0.2140654708307288</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3726587579982108</v>
+        <v>0.3686943031258894</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2691387415277575</v>
+        <v>0.2710387415277576</v>
       </c>
       <c r="C96">
-        <v>-154.1899230293494</v>
+        <v>-157.5544042774343</v>
       </c>
       <c r="D96">
-        <v>80.07607697065059</v>
+        <v>79.40059572256568</v>
       </c>
       <c r="E96">
-        <v>150.866</v>
+        <v>153.555</v>
       </c>
       <c r="F96">
-        <v>252.766</v>
+        <v>255.455</v>
       </c>
       <c r="G96">
         <v>18.5</v>
@@ -9153,37 +9153,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M96">
-        <v>59.6022228</v>
+        <v>60.236289</v>
       </c>
       <c r="N96">
-        <v>-37.62722280000001</v>
+        <v>-38.261289</v>
       </c>
       <c r="O96">
-        <v>-9.406805700000001</v>
+        <v>-9.565322250000001</v>
       </c>
       <c r="P96">
-        <v>-28.22041710000001</v>
+        <v>-28.69596675</v>
       </c>
       <c r="Q96">
-        <v>-10.32041710000001</v>
+        <v>-10.79596675000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.131953315781208</v>
+        <v>1.349183978937451</v>
       </c>
       <c r="T96">
-        <v>13.0118368479978</v>
+        <v>15.61420421759737</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09217357578147234</v>
+        <v>0.09120332761535158</v>
       </c>
       <c r="W96">
-        <v>0.2140654708307288</v>
+        <v>0.2142942553483001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3686943031258894</v>
+        <v>0.3648133104614063</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2710387415277576</v>
+        <v>0.2729387415277575</v>
       </c>
       <c r="C97">
-        <v>-157.5544042774343</v>
+        <v>-160.9075848168622</v>
       </c>
       <c r="D97">
-        <v>79.40059572256568</v>
+        <v>78.73641518313782</v>
       </c>
       <c r="E97">
-        <v>153.555</v>
+        <v>156.244</v>
       </c>
       <c r="F97">
-        <v>255.455</v>
+        <v>258.144</v>
       </c>
       <c r="G97">
         <v>18.5</v>
@@ -9235,37 +9235,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M97">
-        <v>60.236289</v>
+        <v>60.87035520000001</v>
       </c>
       <c r="N97">
-        <v>-38.261289</v>
+        <v>-38.89535520000001</v>
       </c>
       <c r="O97">
-        <v>-9.565322250000001</v>
+        <v>-9.723838800000003</v>
       </c>
       <c r="P97">
-        <v>-28.69596675</v>
+        <v>-29.17151640000001</v>
       </c>
       <c r="Q97">
-        <v>-10.79596675000001</v>
+        <v>-11.27151640000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.349183978937451</v>
+        <v>1.675029973671814</v>
       </c>
       <c r="T97">
-        <v>15.61420421759737</v>
+        <v>19.51775527199671</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09120332761535158</v>
+        <v>0.09025329295269166</v>
       </c>
       <c r="W97">
-        <v>0.2142942553483001</v>
+        <v>0.2145182735217553</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3648133104614063</v>
+        <v>0.3610131718107666</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2729387415277575</v>
+        <v>0.2748387415277576</v>
       </c>
       <c r="C98">
-        <v>-160.9075848168621</v>
+        <v>-164.2497458840689</v>
       </c>
       <c r="D98">
-        <v>78.73641518313782</v>
+        <v>78.08325411593107</v>
       </c>
       <c r="E98">
-        <v>156.2439999999999</v>
+        <v>158.933</v>
       </c>
       <c r="F98">
-        <v>258.1439999999999</v>
+        <v>260.833</v>
       </c>
       <c r="G98">
         <v>18.5</v>
@@ -9317,37 +9317,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M98">
-        <v>60.87035519999999</v>
+        <v>61.5044214</v>
       </c>
       <c r="N98">
-        <v>-38.8953552</v>
+        <v>-39.5294214</v>
       </c>
       <c r="O98">
-        <v>-9.723838799999999</v>
+        <v>-9.882355350000001</v>
       </c>
       <c r="P98">
-        <v>-29.1715164</v>
+        <v>-29.64706605</v>
       </c>
       <c r="Q98">
-        <v>-11.2715164</v>
+        <v>-11.74706605</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.67502997367181</v>
+        <v>2.218106631562413</v>
       </c>
       <c r="T98">
-        <v>19.51775527199666</v>
+        <v>26.02367369599555</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09025329295269167</v>
+        <v>0.08932284663359176</v>
       </c>
       <c r="W98">
-        <v>0.2145182735217553</v>
+        <v>0.2147376727637991</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3610131718107668</v>
+        <v>0.357291386534367</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2748387415277576</v>
+        <v>0.2767387415277575</v>
       </c>
       <c r="C99">
-        <v>-164.2497458840689</v>
+        <v>-167.5811594602355</v>
       </c>
       <c r="D99">
-        <v>78.08325411593107</v>
+        <v>77.44084053976445</v>
       </c>
       <c r="E99">
-        <v>158.933</v>
+        <v>161.622</v>
       </c>
       <c r="F99">
-        <v>260.833</v>
+        <v>263.522</v>
       </c>
       <c r="G99">
         <v>18.5</v>
@@ -9399,37 +9399,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M99">
-        <v>61.5044214</v>
+        <v>62.1384876</v>
       </c>
       <c r="N99">
-        <v>-39.5294214</v>
+        <v>-40.1634876</v>
       </c>
       <c r="O99">
-        <v>-9.882355350000001</v>
+        <v>-10.0408719</v>
       </c>
       <c r="P99">
-        <v>-29.64706605</v>
+        <v>-30.1226157</v>
       </c>
       <c r="Q99">
-        <v>-11.74706605</v>
+        <v>-12.22261570000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.218106631562413</v>
+        <v>3.304259947343619</v>
       </c>
       <c r="T99">
-        <v>26.02367369599555</v>
+        <v>39.03551054399333</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08932284663359176</v>
+        <v>0.08841138901488163</v>
       </c>
       <c r="W99">
-        <v>0.2147376727637991</v>
+        <v>0.2149525944702909</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.357291386534367</v>
+        <v>0.3536455560595265</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2767387415277575</v>
+        <v>0.2786387415277576</v>
       </c>
       <c r="C100">
-        <v>-167.5811594602355</v>
+        <v>-170.9020886489097</v>
       </c>
       <c r="D100">
-        <v>77.44084053976445</v>
+        <v>76.80891135109026</v>
       </c>
       <c r="E100">
-        <v>161.622</v>
+        <v>164.311</v>
       </c>
       <c r="F100">
-        <v>263.522</v>
+        <v>266.211</v>
       </c>
       <c r="G100">
         <v>18.5</v>
@@ -9481,37 +9481,37 @@
         <v>21.97499999999999</v>
       </c>
       <c r="M100">
-        <v>62.1384876</v>
+        <v>62.77255379999999</v>
       </c>
       <c r="N100">
-        <v>-40.1634876</v>
+        <v>-40.7975538</v>
       </c>
       <c r="O100">
-        <v>-10.0408719</v>
+        <v>-10.19938845</v>
       </c>
       <c r="P100">
-        <v>-30.1226157</v>
+        <v>-30.59816535</v>
       </c>
       <c r="Q100">
-        <v>-12.22261570000001</v>
+        <v>-12.69816535</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.304259947343619</v>
+        <v>6.562719894687238</v>
       </c>
       <c r="T100">
-        <v>39.03551054399333</v>
+        <v>78.07102108798665</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08841138901488163</v>
+        <v>0.08751834468139799</v>
       </c>
       <c r="W100">
-        <v>0.2149525944702909</v>
+        <v>0.2151631743241264</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3536455560595265</v>
+        <v>0.350073378725592</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2786387415277576</v>
-      </c>
-      <c r="C101">
-        <v>-170.9020886489097</v>
-      </c>
-      <c r="D101">
-        <v>76.80891135109026</v>
-      </c>
-      <c r="E101">
-        <v>164.311</v>
-      </c>
-      <c r="F101">
-        <v>266.211</v>
-      </c>
-      <c r="G101">
-        <v>18.5</v>
-      </c>
-      <c r="H101">
-        <v>167</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>39.87499999999999</v>
-      </c>
-      <c r="K101">
-        <v>17.9</v>
-      </c>
-      <c r="L101">
-        <v>21.97499999999999</v>
-      </c>
-      <c r="M101">
-        <v>62.77255379999999</v>
-      </c>
-      <c r="N101">
-        <v>-40.7975538</v>
-      </c>
-      <c r="O101">
-        <v>-10.19938845</v>
-      </c>
-      <c r="P101">
-        <v>-30.59816535</v>
-      </c>
-      <c r="Q101">
-        <v>-12.69816535</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.562719894687238</v>
-      </c>
-      <c r="T101">
-        <v>78.07102108798665</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08751834468139799</v>
-      </c>
-      <c r="W101">
-        <v>0.2151631743241264</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.350073378725592</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
